--- a/出勤簿_R8.1-R8.3.xlsx
+++ b/出勤簿_R8.1-R8.3.xlsx
@@ -45,7 +45,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +65,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7F0FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -104,15 +109,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,10 +152,19 @@
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -556,15 +570,15 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <f>COUNTIF('R8.1'!F4:F34,"&gt;0")&amp;"日"</f>
+        <f>COUNTIF('R8.1'!J4:J34,"&gt;0")&amp;"日"</f>
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIF('R8.2'!F4:F31,"&gt;0")&amp;"日"</f>
+        <f>COUNTIF('R8.2'!J4:J31,"&gt;0")&amp;"日"</f>
         <v/>
       </c>
       <c r="D2" s="2">
-        <f>COUNTIF('R8.3'!F4:F34,"&gt;0")&amp;"日"</f>
+        <f>COUNTIF('R8.3'!J4:J34,"&gt;0")&amp;"日"</f>
         <v/>
       </c>
     </row>
@@ -575,15 +589,15 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>SUM('R8.1'!F4:F34)</f>
+        <f>'R8.1'!E36</f>
         <v/>
       </c>
       <c r="C3" s="3">
-        <f>SUM('R8.2'!F4:F31)</f>
+        <f>'R8.2'!E33</f>
         <v/>
       </c>
       <c r="D3" s="3">
-        <f>SUM('R8.3'!F4:F34)</f>
+        <f>'R8.3'!E36</f>
         <v/>
       </c>
     </row>
@@ -594,15 +608,15 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>SUM('R8.1'!G4:G34)</f>
+        <f>SUMPRODUCT((WEEKDAY('R8.1'!A4:A34,2)=7)*'R8.1'!J4:J34)</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>SUM('R8.2'!G4:G31)</f>
+        <f>SUMPRODUCT((WEEKDAY('R8.2'!A4:A31,2)=7)*'R8.2'!J4:J31)</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>SUM('R8.3'!G4:G34)</f>
+        <f>SUMPRODUCT((WEEKDAY('R8.3'!A4:A34,2)=7)*'R8.3'!J4:J34)</f>
         <v/>
       </c>
     </row>
@@ -613,15 +627,15 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>SUM('R8.1'!H4:H34)</f>
+        <f>SUM('R8.1'!F4:F34)</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>SUM('R8.2'!H4:H31)</f>
+        <f>SUM('R8.2'!F4:F31)</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>SUM('R8.3'!H4:H34)</f>
+        <f>SUM('R8.3'!F4:F34)</f>
         <v/>
       </c>
     </row>
@@ -632,15 +646,15 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>SUM('R8.1'!I4:I34)</f>
+        <f>SUM('R8.1'!K4:K34)</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>SUM('R8.2'!I4:I31)</f>
+        <f>SUM('R8.2'!K4:K31)</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>SUM('R8.3'!I4:I34)</f>
+        <f>SUM('R8.3'!K4:K34)</f>
         <v/>
       </c>
     </row>
@@ -655,20 +669,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="10" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="10" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -681,7 +695,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>※ 緑色セル(始業・終業)を編集すると 休憩・労働時間・残業・深夜・合計が自動再計算されます</t>
+          <t>※ 緑色の「出社」「退社」を編集すると、通常/残業/休憩/合計が自動再計算されます</t>
         </is>
       </c>
     </row>
@@ -698,47 +712,47 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>始業</t>
+          <t>出社</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>終業</t>
+          <t>退社</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>残業</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
           <t>休憩</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>労働時間</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>休日労働時間</t>
-        </is>
-      </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>時間外労働時間</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>深夜労働時間</t>
+          <t>週開始</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>総労働</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>週開始(月)</t>
+          <t>深夜</t>
         </is>
       </c>
     </row>
@@ -753,31 +767,32 @@
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="9">
-        <f>IFERROR(IF(D4-C4&gt;TIME(9,0,0),TIME(1,0,0),IF(D4-C4&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A4,2)&gt;=6,J4=0),"",MIN(TIME(8,0,0),J4-F4))</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,D4-C4-E4),0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9">
-        <f>IFERROR(MIN(F4,MAX(0,SUMIFS(F$4:F4,K$4:K4,K4)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="9">
-        <f>IFERROR(IF(F4=0,0,MAX(0,MIN(D4,29/24)-MAX(C4,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
+        <f>IFERROR(MIN(J4,MAX(0,SUMIFS(J$4:J4,I$4:I4,I4)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="9">
+        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,IF(D4-C4&gt;TIME(9,0,0),TIME(1,0,0),IF(D4-C4&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>元日</t>
         </is>
       </c>
-      <c r="K4" s="6">
+      <c r="I4" s="6">
         <f>IFERROR(A4-WEEKDAY(A4,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="9">
+        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,D4-C4-G4),0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="9">
+        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,MAX(0,MIN(D4,29/24)-MAX(C4,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -796,35 +811,36 @@
         <v>0.59375</v>
       </c>
       <c r="E5" s="12">
-        <f>IFERROR(IF(D5-C5&gt;TIME(9,0,0),TIME(1,0,0),IF(D5-C5&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A5,2)&gt;=6,J5=0),"",MIN(TIME(8,0,0),J5-F5))</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,D5-C5-E5),0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="12">
-        <f>IFERROR(MIN(F5,MAX(0,SUMIFS(F$4:F5,K$4:K5,K5)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I5" s="12">
-        <f>IFERROR(IF(F5=0,0,MAX(0,MIN(D5,29/24)-MAX(C5,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J5" s="11" t="inlineStr"/>
-      <c r="K5" s="10">
+        <f>IFERROR(MIN(J5,MAX(0,SUMIFS(J$4:J5,I$4:I5,I5)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="12">
+        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,IF(D5-C5&gt;TIME(9,0,0),TIME(1,0,0),IF(D5-C5&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="11" t="inlineStr"/>
+      <c r="I5" s="10">
         <f>IFERROR(A5-WEEKDAY(A5,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J5" s="12">
+        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,D5-C5-G5),0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="12">
+        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,MAX(0,MIN(D5,29/24)-MAX(C5,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="13" t="n">
         <v>46025</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="14">
         <f>TEXT(A6,"aaa")</f>
         <v/>
       </c>
@@ -834,67 +850,69 @@
       <c r="D6" s="8" t="n">
         <v>0.59375</v>
       </c>
-      <c r="E6" s="12">
-        <f>IFERROR(IF(D6-C6&gt;TIME(9,0,0),TIME(1,0,0),IF(D6-C6&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
-        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,D6-C6-E6),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12">
-        <f>IFERROR(MIN(F6,MAX(0,SUMIFS(F$4:F6,K$4:K6,K6)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="12">
-        <f>IFERROR(IF(F6=0,0,MAX(0,MIN(D6,29/24)-MAX(C6,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J6" s="11" t="inlineStr"/>
-      <c r="K6" s="10">
+      <c r="E6" s="15">
+        <f>IF(OR(WEEKDAY(A6,2)&gt;=6,J6=0),"",MIN(TIME(8,0,0),J6-F6))</f>
+        <v/>
+      </c>
+      <c r="F6" s="15">
+        <f>IFERROR(MIN(J6,MAX(0,SUMIFS(J$4:J6,I$4:I6,I6)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="15">
+        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,IF(D6-C6&gt;TIME(9,0,0),TIME(1,0,0),IF(D6-C6&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="14" t="inlineStr"/>
+      <c r="I6" s="13">
         <f>IFERROR(A6-WEEKDAY(A6,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J6" s="15">
+        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,D6-C6-G6),0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="15">
+        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,MAX(0,MIN(D6,29/24)-MAX(C6,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="16" t="n">
         <v>46026</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="17">
         <f>TEXT(A7,"aaa")</f>
         <v/>
       </c>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="15">
-        <f>IFERROR(IF(D7-C7&gt;TIME(9,0,0),TIME(1,0,0),IF(D7-C7&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="15">
-        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,D7-C7-E7),0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="15">
-        <f>IFERROR(MIN(F7,MAX(0,SUMIFS(F$4:F7,K$4:K7,K7)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="15">
-        <f>IFERROR(IF(F7=0,0,MAX(0,MIN(D7,29/24)-MAX(C7,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="E7" s="18">
+        <f>IF(OR(WEEKDAY(A7,2)&gt;=6,J7=0),"",MIN(TIME(8,0,0),J7-F7))</f>
+        <v/>
+      </c>
+      <c r="F7" s="18">
+        <f>IFERROR(MIN(J7,MAX(0,SUMIFS(J$4:J7,I$4:I7,I7)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="18">
+        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,IF(D7-C7&gt;TIME(9,0,0),TIME(1,0,0),IF(D7-C7&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K7" s="13">
+      <c r="I7" s="16">
         <f>IFERROR(A7-WEEKDAY(A7,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="18">
+        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,D7-C7-G7),0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="18">
+        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,MAX(0,MIN(D7,29/24)-MAX(C7,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -913,27 +931,28 @@
         <v>0.6458333333333334</v>
       </c>
       <c r="E8" s="12">
-        <f>IFERROR(IF(D8-C8&gt;TIME(9,0,0),TIME(1,0,0),IF(D8-C8&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A8,2)&gt;=6,J8=0),"",MIN(TIME(8,0,0),J8-F8))</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,D8-C8-E8),0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12">
-        <f>IFERROR(MIN(F8,MAX(0,SUMIFS(F$4:F8,K$4:K8,K8)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="12">
-        <f>IFERROR(IF(F8=0,0,MAX(0,MIN(D8,29/24)-MAX(C8,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="11" t="inlineStr"/>
-      <c r="K8" s="10">
+        <f>IFERROR(MIN(J8,MAX(0,SUMIFS(J$4:J8,I$4:I8,I8)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,IF(D8-C8&gt;TIME(9,0,0),TIME(1,0,0),IF(D8-C8&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="11" t="inlineStr"/>
+      <c r="I8" s="10">
         <f>IFERROR(A8-WEEKDAY(A8,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,D8-C8-G8),0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,MAX(0,MIN(D8,29/24)-MAX(C8,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -952,27 +971,28 @@
         <v>0.6458333333333334</v>
       </c>
       <c r="E9" s="12">
-        <f>IFERROR(IF(D9-C9&gt;TIME(9,0,0),TIME(1,0,0),IF(D9-C9&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A9,2)&gt;=6,J9=0),"",MIN(TIME(8,0,0),J9-F9))</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,D9-C9-E9),0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12">
-        <f>IFERROR(MIN(F9,MAX(0,SUMIFS(F$4:F9,K$4:K9,K9)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I9" s="12">
-        <f>IFERROR(IF(F9=0,0,MAX(0,MIN(D9,29/24)-MAX(C9,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J9" s="11" t="inlineStr"/>
-      <c r="K9" s="10">
+        <f>IFERROR(MIN(J9,MAX(0,SUMIFS(J$4:J9,I$4:I9,I9)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="12">
+        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,IF(D9-C9&gt;TIME(9,0,0),TIME(1,0,0),IF(D9-C9&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="11" t="inlineStr"/>
+      <c r="I9" s="10">
         <f>IFERROR(A9-WEEKDAY(A9,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="12">
+        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,D9-C9-G9),0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="12">
+        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,MAX(0,MIN(D9,29/24)-MAX(C9,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -991,27 +1011,28 @@
         <v>0.6458333333333334</v>
       </c>
       <c r="E10" s="12">
-        <f>IFERROR(IF(D10-C10&gt;TIME(9,0,0),TIME(1,0,0),IF(D10-C10&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A10,2)&gt;=6,J10=0),"",MIN(TIME(8,0,0),J10-F10))</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,D10-C10-E10),0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12">
-        <f>IFERROR(MIN(F10,MAX(0,SUMIFS(F$4:F10,K$4:K10,K10)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I10" s="12">
-        <f>IFERROR(IF(F10=0,0,MAX(0,MIN(D10,29/24)-MAX(C10,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J10" s="11" t="inlineStr"/>
-      <c r="K10" s="10">
+        <f>IFERROR(MIN(J10,MAX(0,SUMIFS(J$4:J10,I$4:I10,I10)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="12">
+        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,IF(D10-C10&gt;TIME(9,0,0),TIME(1,0,0),IF(D10-C10&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="11" t="inlineStr"/>
+      <c r="I10" s="10">
         <f>IFERROR(A10-WEEKDAY(A10,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="12">
+        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,D10-C10-G10),0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="12">
+        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,MAX(0,MIN(D10,29/24)-MAX(C10,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1030,27 +1051,28 @@
         <v>0.6458333333333334</v>
       </c>
       <c r="E11" s="12">
-        <f>IFERROR(IF(D11-C11&gt;TIME(9,0,0),TIME(1,0,0),IF(D11-C11&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A11,2)&gt;=6,J11=0),"",MIN(TIME(8,0,0),J11-F11))</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,D11-C11-E11),0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="12">
-        <f>IFERROR(MIN(F11,MAX(0,SUMIFS(F$4:F11,K$4:K11,K11)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I11" s="12">
-        <f>IFERROR(IF(F11=0,0,MAX(0,MIN(D11,29/24)-MAX(C11,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="11" t="inlineStr"/>
-      <c r="K11" s="10">
+        <f>IFERROR(MIN(J11,MAX(0,SUMIFS(J$4:J11,I$4:I11,I11)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="12">
+        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,IF(D11-C11&gt;TIME(9,0,0),TIME(1,0,0),IF(D11-C11&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="11" t="inlineStr"/>
+      <c r="I11" s="10">
         <f>IFERROR(A11-WEEKDAY(A11,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="12">
+        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,D11-C11-G11),0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="12">
+        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,MAX(0,MIN(D11,29/24)-MAX(C11,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1069,35 +1091,36 @@
         <v>0.6458333333333334</v>
       </c>
       <c r="E12" s="12">
-        <f>IFERROR(IF(D12-C12&gt;TIME(9,0,0),TIME(1,0,0),IF(D12-C12&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A12,2)&gt;=6,J12=0),"",MIN(TIME(8,0,0),J12-F12))</f>
         <v/>
       </c>
       <c r="F12" s="12">
-        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,D12-C12-E12),0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <f>IFERROR(MIN(F12,MAX(0,SUMIFS(F$4:F12,K$4:K12,K12)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="12">
-        <f>IFERROR(IF(F12=0,0,MAX(0,MIN(D12,29/24)-MAX(C12,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
-      <c r="K12" s="10">
+        <f>IFERROR(MIN(J12,MAX(0,SUMIFS(J$4:J12,I$4:I12,I12)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="12">
+        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,IF(D12-C12&gt;TIME(9,0,0),TIME(1,0,0),IF(D12-C12&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="10">
         <f>IFERROR(A12-WEEKDAY(A12,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J12" s="12">
+        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,D12-C12-G12),0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="12">
+        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,MAX(0,MIN(D12,29/24)-MAX(C12,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="13" t="n">
         <v>46032</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="14">
         <f>TEXT(A13,"aaa")</f>
         <v/>
       </c>
@@ -1107,67 +1130,69 @@
       <c r="D13" s="8" t="n">
         <v>0.6458333333333334</v>
       </c>
-      <c r="E13" s="12">
-        <f>IFERROR(IF(D13-C13&gt;TIME(9,0,0),TIME(1,0,0),IF(D13-C13&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
-        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,D13-C13-E13),0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <f>IFERROR(MIN(F13,MAX(0,SUMIFS(F$4:F13,K$4:K13,K13)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="12">
-        <f>IFERROR(IF(F13=0,0,MAX(0,MIN(D13,29/24)-MAX(C13,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J13" s="11" t="inlineStr"/>
-      <c r="K13" s="10">
+      <c r="E13" s="15">
+        <f>IF(OR(WEEKDAY(A13,2)&gt;=6,J13=0),"",MIN(TIME(8,0,0),J13-F13))</f>
+        <v/>
+      </c>
+      <c r="F13" s="15">
+        <f>IFERROR(MIN(J13,MAX(0,SUMIFS(J$4:J13,I$4:I13,I13)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="15">
+        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,IF(D13-C13&gt;TIME(9,0,0),TIME(1,0,0),IF(D13-C13&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="13">
         <f>IFERROR(A13-WEEKDAY(A13,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J13" s="15">
+        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,D13-C13-G13),0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="15">
+        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,MAX(0,MIN(D13,29/24)-MAX(C13,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="n">
+      <c r="A14" s="16" t="n">
         <v>46033</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="17">
         <f>TEXT(A14,"aaa")</f>
         <v/>
       </c>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="15">
-        <f>IFERROR(IF(D14-C14&gt;TIME(9,0,0),TIME(1,0,0),IF(D14-C14&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="15">
-        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,D14-C14-E14),0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="15">
-        <f>IFERROR(MIN(F14,MAX(0,SUMIFS(F$4:F14,K$4:K14,K14)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="15">
-        <f>IFERROR(IF(F14=0,0,MAX(0,MIN(D14,29/24)-MAX(C14,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="E14" s="18">
+        <f>IF(OR(WEEKDAY(A14,2)&gt;=6,J14=0),"",MIN(TIME(8,0,0),J14-F14))</f>
+        <v/>
+      </c>
+      <c r="F14" s="18">
+        <f>IFERROR(MIN(J14,MAX(0,SUMIFS(J$4:J14,I$4:I14,I14)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="18">
+        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,IF(D14-C14&gt;TIME(9,0,0),TIME(1,0,0),IF(D14-C14&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K14" s="13">
+      <c r="I14" s="16">
         <f>IFERROR(A14-WEEKDAY(A14,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="18">
+        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,D14-C14-G14),0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="18">
+        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,MAX(0,MIN(D14,29/24)-MAX(C14,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1182,31 +1207,32 @@
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="9">
-        <f>IFERROR(IF(D15-C15&gt;TIME(9,0,0),TIME(1,0,0),IF(D15-C15&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A15,2)&gt;=6,J15=0),"",MIN(TIME(8,0,0),J15-F15))</f>
         <v/>
       </c>
       <c r="F15" s="9">
-        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,D15-C15-E15),0)</f>
-        <v/>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="9">
-        <f>IFERROR(MIN(F15,MAX(0,SUMIFS(F$4:F15,K$4:K15,K15)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I15" s="9">
-        <f>IFERROR(IF(F15=0,0,MAX(0,MIN(D15,29/24)-MAX(C15,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+        <f>IFERROR(MIN(J15,MAX(0,SUMIFS(J$4:J15,I$4:I15,I15)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="9">
+        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,IF(D15-C15&gt;TIME(9,0,0),TIME(1,0,0),IF(D15-C15&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>成人の日</t>
         </is>
       </c>
-      <c r="K15" s="6">
+      <c r="I15" s="6">
         <f>IFERROR(A15-WEEKDAY(A15,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="9">
+        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,D15-C15-G15),0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="9">
+        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,MAX(0,MIN(D15,29/24)-MAX(C15,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1225,27 +1251,28 @@
         <v>0.59375</v>
       </c>
       <c r="E16" s="12">
-        <f>IFERROR(IF(D16-C16&gt;TIME(9,0,0),TIME(1,0,0),IF(D16-C16&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A16,2)&gt;=6,J16=0),"",MIN(TIME(8,0,0),J16-F16))</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,D16-C16-E16),0)</f>
-        <v/>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="12">
-        <f>IFERROR(MIN(F16,MAX(0,SUMIFS(F$4:F16,K$4:K16,K16)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="12">
-        <f>IFERROR(IF(F16=0,0,MAX(0,MIN(D16,29/24)-MAX(C16,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J16" s="11" t="inlineStr"/>
-      <c r="K16" s="10">
+        <f>IFERROR(MIN(J16,MAX(0,SUMIFS(J$4:J16,I$4:I16,I16)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="12">
+        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,IF(D16-C16&gt;TIME(9,0,0),TIME(1,0,0),IF(D16-C16&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="11" t="inlineStr"/>
+      <c r="I16" s="10">
         <f>IFERROR(A16-WEEKDAY(A16,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="12">
+        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,D16-C16-G16),0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="12">
+        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,MAX(0,MIN(D16,29/24)-MAX(C16,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1264,27 +1291,28 @@
         <v>0.59375</v>
       </c>
       <c r="E17" s="12">
-        <f>IFERROR(IF(D17-C17&gt;TIME(9,0,0),TIME(1,0,0),IF(D17-C17&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A17,2)&gt;=6,J17=0),"",MIN(TIME(8,0,0),J17-F17))</f>
         <v/>
       </c>
       <c r="F17" s="12">
-        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,D17-C17-E17),0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="12">
-        <f>IFERROR(MIN(F17,MAX(0,SUMIFS(F$4:F17,K$4:K17,K17)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="12">
-        <f>IFERROR(IF(F17=0,0,MAX(0,MIN(D17,29/24)-MAX(C17,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J17" s="11" t="inlineStr"/>
-      <c r="K17" s="10">
+        <f>IFERROR(MIN(J17,MAX(0,SUMIFS(J$4:J17,I$4:I17,I17)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="12">
+        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,IF(D17-C17&gt;TIME(9,0,0),TIME(1,0,0),IF(D17-C17&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="11" t="inlineStr"/>
+      <c r="I17" s="10">
         <f>IFERROR(A17-WEEKDAY(A17,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="12">
+        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,D17-C17-G17),0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="12">
+        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,MAX(0,MIN(D17,29/24)-MAX(C17,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1303,27 +1331,28 @@
         <v>0.59375</v>
       </c>
       <c r="E18" s="12">
-        <f>IFERROR(IF(D18-C18&gt;TIME(9,0,0),TIME(1,0,0),IF(D18-C18&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A18,2)&gt;=6,J18=0),"",MIN(TIME(8,0,0),J18-F18))</f>
         <v/>
       </c>
       <c r="F18" s="12">
-        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,D18-C18-E18),0)</f>
-        <v/>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="12">
-        <f>IFERROR(MIN(F18,MAX(0,SUMIFS(F$4:F18,K$4:K18,K18)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I18" s="12">
-        <f>IFERROR(IF(F18=0,0,MAX(0,MIN(D18,29/24)-MAX(C18,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J18" s="11" t="inlineStr"/>
-      <c r="K18" s="10">
+        <f>IFERROR(MIN(J18,MAX(0,SUMIFS(J$4:J18,I$4:I18,I18)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="12">
+        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,IF(D18-C18&gt;TIME(9,0,0),TIME(1,0,0),IF(D18-C18&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="11" t="inlineStr"/>
+      <c r="I18" s="10">
         <f>IFERROR(A18-WEEKDAY(A18,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="12">
+        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,D18-C18-G18),0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="12">
+        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,MAX(0,MIN(D18,29/24)-MAX(C18,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1342,35 +1371,36 @@
         <v>0.59375</v>
       </c>
       <c r="E19" s="12">
-        <f>IFERROR(IF(D19-C19&gt;TIME(9,0,0),TIME(1,0,0),IF(D19-C19&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A19,2)&gt;=6,J19=0),"",MIN(TIME(8,0,0),J19-F19))</f>
         <v/>
       </c>
       <c r="F19" s="12">
-        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,D19-C19-E19),0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12">
-        <f>IFERROR(MIN(F19,MAX(0,SUMIFS(F$4:F19,K$4:K19,K19)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I19" s="12">
-        <f>IFERROR(IF(F19=0,0,MAX(0,MIN(D19,29/24)-MAX(C19,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="11" t="inlineStr"/>
-      <c r="K19" s="10">
+        <f>IFERROR(MIN(J19,MAX(0,SUMIFS(J$4:J19,I$4:I19,I19)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="12">
+        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,IF(D19-C19&gt;TIME(9,0,0),TIME(1,0,0),IF(D19-C19&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="10">
         <f>IFERROR(A19-WEEKDAY(A19,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J19" s="12">
+        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,D19-C19-G19),0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="12">
+        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,MAX(0,MIN(D19,29/24)-MAX(C19,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="13" t="n">
         <v>46039</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="14">
         <f>TEXT(A20,"aaa")</f>
         <v/>
       </c>
@@ -1380,67 +1410,69 @@
       <c r="D20" s="8" t="n">
         <v>0.59375</v>
       </c>
-      <c r="E20" s="12">
-        <f>IFERROR(IF(D20-C20&gt;TIME(9,0,0),TIME(1,0,0),IF(D20-C20&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F20" s="12">
-        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,D20-C20-E20),0)</f>
-        <v/>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="12">
-        <f>IFERROR(MIN(F20,MAX(0,SUMIFS(F$4:F20,K$4:K20,K20)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I20" s="12">
-        <f>IFERROR(IF(F20=0,0,MAX(0,MIN(D20,29/24)-MAX(C20,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="10">
+      <c r="E20" s="15">
+        <f>IF(OR(WEEKDAY(A20,2)&gt;=6,J20=0),"",MIN(TIME(8,0,0),J20-F20))</f>
+        <v/>
+      </c>
+      <c r="F20" s="15">
+        <f>IFERROR(MIN(J20,MAX(0,SUMIFS(J$4:J20,I$4:I20,I20)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="15">
+        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,IF(D20-C20&gt;TIME(9,0,0),TIME(1,0,0),IF(D20-C20&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="14" t="inlineStr"/>
+      <c r="I20" s="13">
         <f>IFERROR(A20-WEEKDAY(A20,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J20" s="15">
+        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,D20-C20-G20),0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="15">
+        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,MAX(0,MIN(D20,29/24)-MAX(C20,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="n">
+      <c r="A21" s="16" t="n">
         <v>46040</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="17">
         <f>TEXT(A21,"aaa")</f>
         <v/>
       </c>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15">
-        <f>IFERROR(IF(D21-C21&gt;TIME(9,0,0),TIME(1,0,0),IF(D21-C21&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F21" s="15">
-        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,D21-C21-E21),0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="15">
-        <f>IFERROR(MIN(F21,MAX(0,SUMIFS(F$4:F21,K$4:K21,K21)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="15">
-        <f>IFERROR(IF(F21=0,0,MAX(0,MIN(D21,29/24)-MAX(C21,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="E21" s="18">
+        <f>IF(OR(WEEKDAY(A21,2)&gt;=6,J21=0),"",MIN(TIME(8,0,0),J21-F21))</f>
+        <v/>
+      </c>
+      <c r="F21" s="18">
+        <f>IFERROR(MIN(J21,MAX(0,SUMIFS(J$4:J21,I$4:I21,I21)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="18">
+        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,IF(D21-C21&gt;TIME(9,0,0),TIME(1,0,0),IF(D21-C21&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K21" s="13">
+      <c r="I21" s="16">
         <f>IFERROR(A21-WEEKDAY(A21,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="18">
+        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,D21-C21-G21),0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="18">
+        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,MAX(0,MIN(D21,29/24)-MAX(C21,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1459,27 +1491,28 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="E22" s="12">
-        <f>IFERROR(IF(D22-C22&gt;TIME(9,0,0),TIME(1,0,0),IF(D22-C22&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A22,2)&gt;=6,J22=0),"",MIN(TIME(8,0,0),J22-F22))</f>
         <v/>
       </c>
       <c r="F22" s="12">
-        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,D22-C22-E22),0)</f>
-        <v/>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="12">
-        <f>IFERROR(MIN(F22,MAX(0,SUMIFS(F$4:F22,K$4:K22,K22)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="12">
-        <f>IFERROR(IF(F22=0,0,MAX(0,MIN(D22,29/24)-MAX(C22,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="11" t="inlineStr"/>
-      <c r="K22" s="10">
+        <f>IFERROR(MIN(J22,MAX(0,SUMIFS(J$4:J22,I$4:I22,I22)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="12">
+        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,IF(D22-C22&gt;TIME(9,0,0),TIME(1,0,0),IF(D22-C22&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="11" t="inlineStr"/>
+      <c r="I22" s="10">
         <f>IFERROR(A22-WEEKDAY(A22,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,D22-C22-G22),0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="12">
+        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,MAX(0,MIN(D22,29/24)-MAX(C22,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1498,27 +1531,28 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="E23" s="12">
-        <f>IFERROR(IF(D23-C23&gt;TIME(9,0,0),TIME(1,0,0),IF(D23-C23&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A23,2)&gt;=6,J23=0),"",MIN(TIME(8,0,0),J23-F23))</f>
         <v/>
       </c>
       <c r="F23" s="12">
-        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,D23-C23-E23),0)</f>
-        <v/>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="12">
-        <f>IFERROR(MIN(F23,MAX(0,SUMIFS(F$4:F23,K$4:K23,K23)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I23" s="12">
-        <f>IFERROR(IF(F23=0,0,MAX(0,MIN(D23,29/24)-MAX(C23,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="10">
+        <f>IFERROR(MIN(J23,MAX(0,SUMIFS(J$4:J23,I$4:I23,I23)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="12">
+        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,IF(D23-C23&gt;TIME(9,0,0),TIME(1,0,0),IF(D23-C23&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="11" t="inlineStr"/>
+      <c r="I23" s="10">
         <f>IFERROR(A23-WEEKDAY(A23,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="12">
+        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,D23-C23-G23),0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="12">
+        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,MAX(0,MIN(D23,29/24)-MAX(C23,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1537,27 +1571,28 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="E24" s="12">
-        <f>IFERROR(IF(D24-C24&gt;TIME(9,0,0),TIME(1,0,0),IF(D24-C24&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A24,2)&gt;=6,J24=0),"",MIN(TIME(8,0,0),J24-F24))</f>
         <v/>
       </c>
       <c r="F24" s="12">
-        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,D24-C24-E24),0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="12">
-        <f>IFERROR(MIN(F24,MAX(0,SUMIFS(F$4:F24,K$4:K24,K24)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I24" s="12">
-        <f>IFERROR(IF(F24=0,0,MAX(0,MIN(D24,29/24)-MAX(C24,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="10">
+        <f>IFERROR(MIN(J24,MAX(0,SUMIFS(J$4:J24,I$4:I24,I24)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="12">
+        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,IF(D24-C24&gt;TIME(9,0,0),TIME(1,0,0),IF(D24-C24&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="11" t="inlineStr"/>
+      <c r="I24" s="10">
         <f>IFERROR(A24-WEEKDAY(A24,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="12">
+        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,D24-C24-G24),0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="12">
+        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,MAX(0,MIN(D24,29/24)-MAX(C24,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1576,27 +1611,28 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="E25" s="12">
-        <f>IFERROR(IF(D25-C25&gt;TIME(9,0,0),TIME(1,0,0),IF(D25-C25&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A25,2)&gt;=6,J25=0),"",MIN(TIME(8,0,0),J25-F25))</f>
         <v/>
       </c>
       <c r="F25" s="12">
-        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,D25-C25-E25),0)</f>
-        <v/>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="12">
-        <f>IFERROR(MIN(F25,MAX(0,SUMIFS(F$4:F25,K$4:K25,K25)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I25" s="12">
-        <f>IFERROR(IF(F25=0,0,MAX(0,MIN(D25,29/24)-MAX(C25,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="10">
+        <f>IFERROR(MIN(J25,MAX(0,SUMIFS(J$4:J25,I$4:I25,I25)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="12">
+        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,IF(D25-C25&gt;TIME(9,0,0),TIME(1,0,0),IF(D25-C25&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="11" t="inlineStr"/>
+      <c r="I25" s="10">
         <f>IFERROR(A25-WEEKDAY(A25,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="12">
+        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,D25-C25-G25),0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="12">
+        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,MAX(0,MIN(D25,29/24)-MAX(C25,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1615,35 +1651,36 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="E26" s="12">
-        <f>IFERROR(IF(D26-C26&gt;TIME(9,0,0),TIME(1,0,0),IF(D26-C26&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A26,2)&gt;=6,J26=0),"",MIN(TIME(8,0,0),J26-F26))</f>
         <v/>
       </c>
       <c r="F26" s="12">
-        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,D26-C26-E26),0)</f>
-        <v/>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="12">
-        <f>IFERROR(MIN(F26,MAX(0,SUMIFS(F$4:F26,K$4:K26,K26)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I26" s="12">
-        <f>IFERROR(IF(F26=0,0,MAX(0,MIN(D26,29/24)-MAX(C26,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J26" s="11" t="inlineStr"/>
-      <c r="K26" s="10">
+        <f>IFERROR(MIN(J26,MAX(0,SUMIFS(J$4:J26,I$4:I26,I26)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="12">
+        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,IF(D26-C26&gt;TIME(9,0,0),TIME(1,0,0),IF(D26-C26&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="11" t="inlineStr"/>
+      <c r="I26" s="10">
         <f>IFERROR(A26-WEEKDAY(A26,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J26" s="12">
+        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,D26-C26-G26),0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="12">
+        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,MAX(0,MIN(D26,29/24)-MAX(C26,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="13" t="n">
         <v>46046</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="14">
         <f>TEXT(A27,"aaa")</f>
         <v/>
       </c>
@@ -1653,67 +1690,69 @@
       <c r="D27" s="8" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="E27" s="12">
-        <f>IFERROR(IF(D27-C27&gt;TIME(9,0,0),TIME(1,0,0),IF(D27-C27&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F27" s="12">
-        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,D27-C27-E27),0)</f>
-        <v/>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="12">
-        <f>IFERROR(MIN(F27,MAX(0,SUMIFS(F$4:F27,K$4:K27,K27)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I27" s="12">
-        <f>IFERROR(IF(F27=0,0,MAX(0,MIN(D27,29/24)-MAX(C27,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
-      <c r="K27" s="10">
+      <c r="E27" s="15">
+        <f>IF(OR(WEEKDAY(A27,2)&gt;=6,J27=0),"",MIN(TIME(8,0,0),J27-F27))</f>
+        <v/>
+      </c>
+      <c r="F27" s="15">
+        <f>IFERROR(MIN(J27,MAX(0,SUMIFS(J$4:J27,I$4:I27,I27)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="15">
+        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,IF(D27-C27&gt;TIME(9,0,0),TIME(1,0,0),IF(D27-C27&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="14" t="inlineStr"/>
+      <c r="I27" s="13">
         <f>IFERROR(A27-WEEKDAY(A27,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J27" s="15">
+        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,D27-C27-G27),0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="15">
+        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,MAX(0,MIN(D27,29/24)-MAX(C27,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="n">
+      <c r="A28" s="16" t="n">
         <v>46047</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="17">
         <f>TEXT(A28,"aaa")</f>
         <v/>
       </c>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
-      <c r="E28" s="15">
-        <f>IFERROR(IF(D28-C28&gt;TIME(9,0,0),TIME(1,0,0),IF(D28-C28&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F28" s="15">
-        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,D28-C28-E28),0)</f>
-        <v/>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="15">
-        <f>IFERROR(MIN(F28,MAX(0,SUMIFS(F$4:F28,K$4:K28,K28)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I28" s="15">
-        <f>IFERROR(IF(F28=0,0,MAX(0,MIN(D28,29/24)-MAX(C28,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="E28" s="18">
+        <f>IF(OR(WEEKDAY(A28,2)&gt;=6,J28=0),"",MIN(TIME(8,0,0),J28-F28))</f>
+        <v/>
+      </c>
+      <c r="F28" s="18">
+        <f>IFERROR(MIN(J28,MAX(0,SUMIFS(J$4:J28,I$4:I28,I28)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="18">
+        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,IF(D28-C28&gt;TIME(9,0,0),TIME(1,0,0),IF(D28-C28&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K28" s="13">
+      <c r="I28" s="16">
         <f>IFERROR(A28-WEEKDAY(A28,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="18">
+        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,D28-C28-G28),0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="18">
+        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,MAX(0,MIN(D28,29/24)-MAX(C28,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1732,27 +1771,28 @@
         <v>0.5347222222222222</v>
       </c>
       <c r="E29" s="12">
-        <f>IFERROR(IF(D29-C29&gt;TIME(9,0,0),TIME(1,0,0),IF(D29-C29&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A29,2)&gt;=6,J29=0),"",MIN(TIME(8,0,0),J29-F29))</f>
         <v/>
       </c>
       <c r="F29" s="12">
-        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,D29-C29-E29),0)</f>
-        <v/>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="12">
-        <f>IFERROR(MIN(F29,MAX(0,SUMIFS(F$4:F29,K$4:K29,K29)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I29" s="12">
-        <f>IFERROR(IF(F29=0,0,MAX(0,MIN(D29,29/24)-MAX(C29,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J29" s="11" t="inlineStr"/>
-      <c r="K29" s="10">
+        <f>IFERROR(MIN(J29,MAX(0,SUMIFS(J$4:J29,I$4:I29,I29)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="12">
+        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,IF(D29-C29&gt;TIME(9,0,0),TIME(1,0,0),IF(D29-C29&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="11" t="inlineStr"/>
+      <c r="I29" s="10">
         <f>IFERROR(A29-WEEKDAY(A29,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="12">
+        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,D29-C29-G29),0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="12">
+        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,MAX(0,MIN(D29,29/24)-MAX(C29,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1771,27 +1811,28 @@
         <v>0.5347222222222222</v>
       </c>
       <c r="E30" s="12">
-        <f>IFERROR(IF(D30-C30&gt;TIME(9,0,0),TIME(1,0,0),IF(D30-C30&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A30,2)&gt;=6,J30=0),"",MIN(TIME(8,0,0),J30-F30))</f>
         <v/>
       </c>
       <c r="F30" s="12">
-        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,D30-C30-E30),0)</f>
-        <v/>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="12">
-        <f>IFERROR(MIN(F30,MAX(0,SUMIFS(F$4:F30,K$4:K30,K30)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I30" s="12">
-        <f>IFERROR(IF(F30=0,0,MAX(0,MIN(D30,29/24)-MAX(C30,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J30" s="11" t="inlineStr"/>
-      <c r="K30" s="10">
+        <f>IFERROR(MIN(J30,MAX(0,SUMIFS(J$4:J30,I$4:I30,I30)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="12">
+        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,IF(D30-C30&gt;TIME(9,0,0),TIME(1,0,0),IF(D30-C30&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="11" t="inlineStr"/>
+      <c r="I30" s="10">
         <f>IFERROR(A30-WEEKDAY(A30,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="12">
+        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,D30-C30-G30),0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="12">
+        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,MAX(0,MIN(D30,29/24)-MAX(C30,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1810,27 +1851,28 @@
         <v>0.5347222222222222</v>
       </c>
       <c r="E31" s="12">
-        <f>IFERROR(IF(D31-C31&gt;TIME(9,0,0),TIME(1,0,0),IF(D31-C31&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A31,2)&gt;=6,J31=0),"",MIN(TIME(8,0,0),J31-F31))</f>
         <v/>
       </c>
       <c r="F31" s="12">
-        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,D31-C31-E31),0)</f>
-        <v/>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="12">
-        <f>IFERROR(MIN(F31,MAX(0,SUMIFS(F$4:F31,K$4:K31,K31)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I31" s="12">
-        <f>IFERROR(IF(F31=0,0,MAX(0,MIN(D31,29/24)-MAX(C31,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J31" s="11" t="inlineStr"/>
-      <c r="K31" s="10">
+        <f>IFERROR(MIN(J31,MAX(0,SUMIFS(J$4:J31,I$4:I31,I31)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="12">
+        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,IF(D31-C31&gt;TIME(9,0,0),TIME(1,0,0),IF(D31-C31&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="11" t="inlineStr"/>
+      <c r="I31" s="10">
         <f>IFERROR(A31-WEEKDAY(A31,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="12">
+        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,D31-C31-G31),0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="12">
+        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,MAX(0,MIN(D31,29/24)-MAX(C31,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1849,27 +1891,28 @@
         <v>0.5347222222222222</v>
       </c>
       <c r="E32" s="12">
-        <f>IFERROR(IF(D32-C32&gt;TIME(9,0,0),TIME(1,0,0),IF(D32-C32&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A32,2)&gt;=6,J32=0),"",MIN(TIME(8,0,0),J32-F32))</f>
         <v/>
       </c>
       <c r="F32" s="12">
-        <f>IFERROR(IF(OR(C32="",D32="",D32&lt;=C32),0,D32-C32-E32),0)</f>
-        <v/>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="12">
-        <f>IFERROR(MIN(F32,MAX(0,SUMIFS(F$4:F32,K$4:K32,K32)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I32" s="12">
-        <f>IFERROR(IF(F32=0,0,MAX(0,MIN(D32,29/24)-MAX(C32,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J32" s="11" t="inlineStr"/>
-      <c r="K32" s="10">
+        <f>IFERROR(MIN(J32,MAX(0,SUMIFS(J$4:J32,I$4:I32,I32)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="12">
+        <f>IFERROR(IF(OR(C32="",D32="",D32&lt;=C32),0,IF(D32-C32&gt;TIME(9,0,0),TIME(1,0,0),IF(D32-C32&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="11" t="inlineStr"/>
+      <c r="I32" s="10">
         <f>IFERROR(A32-WEEKDAY(A32,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="12">
+        <f>IFERROR(IF(OR(C32="",D32="",D32&lt;=C32),0,D32-C32-G32),0)</f>
+        <v/>
+      </c>
+      <c r="K32" s="12">
+        <f>IFERROR(IF(OR(C32="",D32="",D32&lt;=C32),0,MAX(0,MIN(D32,29/24)-MAX(C32,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -1888,35 +1931,36 @@
         <v>0.5347222222222222</v>
       </c>
       <c r="E33" s="12">
-        <f>IFERROR(IF(D33-C33&gt;TIME(9,0,0),TIME(1,0,0),IF(D33-C33&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A33,2)&gt;=6,J33=0),"",MIN(TIME(8,0,0),J33-F33))</f>
         <v/>
       </c>
       <c r="F33" s="12">
-        <f>IFERROR(IF(OR(C33="",D33="",D33&lt;=C33),0,D33-C33-E33),0)</f>
-        <v/>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="12">
-        <f>IFERROR(MIN(F33,MAX(0,SUMIFS(F$4:F33,K$4:K33,K33)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I33" s="12">
-        <f>IFERROR(IF(F33=0,0,MAX(0,MIN(D33,29/24)-MAX(C33,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J33" s="11" t="inlineStr"/>
-      <c r="K33" s="10">
+        <f>IFERROR(MIN(J33,MAX(0,SUMIFS(J$4:J33,I$4:I33,I33)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="12">
+        <f>IFERROR(IF(OR(C33="",D33="",D33&lt;=C33),0,IF(D33-C33&gt;TIME(9,0,0),TIME(1,0,0),IF(D33-C33&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H33" s="11" t="inlineStr"/>
+      <c r="I33" s="10">
         <f>IFERROR(A33-WEEKDAY(A33,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J33" s="12">
+        <f>IFERROR(IF(OR(C33="",D33="",D33&lt;=C33),0,D33-C33-G33),0)</f>
+        <v/>
+      </c>
+      <c r="K33" s="12">
+        <f>IFERROR(IF(OR(C33="",D33="",D33&lt;=C33),0,MAX(0,MIN(D33,29/24)-MAX(C33,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="13" t="n">
         <v>46053</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="14">
         <f>TEXT(A34,"aaa")</f>
         <v/>
       </c>
@@ -1926,67 +1970,86 @@
       <c r="D34" s="8" t="n">
         <v>0.5347222222222222</v>
       </c>
-      <c r="E34" s="12">
-        <f>IFERROR(IF(D34-C34&gt;TIME(9,0,0),TIME(1,0,0),IF(D34-C34&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F34" s="12">
-        <f>IFERROR(IF(OR(C34="",D34="",D34&lt;=C34),0,D34-C34-E34),0)</f>
-        <v/>
-      </c>
-      <c r="G34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="12">
-        <f>IFERROR(MIN(F34,MAX(0,SUMIFS(F$4:F34,K$4:K34,K34)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I34" s="12">
-        <f>IFERROR(IF(F34=0,0,MAX(0,MIN(D34,29/24)-MAX(C34,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J34" s="11" t="inlineStr"/>
-      <c r="K34" s="10">
+      <c r="E34" s="15">
+        <f>IF(OR(WEEKDAY(A34,2)&gt;=6,J34=0),"",MIN(TIME(8,0,0),J34-F34))</f>
+        <v/>
+      </c>
+      <c r="F34" s="15">
+        <f>IFERROR(MIN(J34,MAX(0,SUMIFS(J$4:J34,I$4:I34,I34)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="15">
+        <f>IFERROR(IF(OR(C34="",D34="",D34&lt;=C34),0,IF(D34-C34&gt;TIME(9,0,0),TIME(1,0,0),IF(D34-C34&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H34" s="14" t="inlineStr"/>
+      <c r="I34" s="13">
         <f>IFERROR(A34-WEEKDAY(A34,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J34" s="15">
+        <f>IFERROR(IF(OR(C34="",D34="",D34&lt;=C34),0,D34-C34-G34),0)</f>
+        <v/>
+      </c>
+      <c r="K34" s="15">
+        <f>IFERROR(IF(OR(C34="",D34="",D34&lt;=C34),0,MAX(0,MIN(D34,29/24)-MAX(C34,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B35" s="16">
-        <f>COUNTIF(F4:F34,"&gt;0")&amp;"日"</f>
-        <v/>
-      </c>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="17">
+      <c r="B35" s="19">
+        <f>COUNTIF(J4:J34,"&gt;0")&amp;"日"</f>
+        <v/>
+      </c>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="20">
+        <f>SUM(E4:E34)</f>
+        <v/>
+      </c>
+      <c r="F35" s="20">
         <f>SUM(F4:F34)</f>
         <v/>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="20">
         <f>SUM(G4:G34)</f>
         <v/>
       </c>
-      <c r="H35" s="17">
-        <f>SUM(H4:H34)</f>
-        <v/>
-      </c>
-      <c r="I35" s="17">
-        <f>SUM(I4:I34)</f>
-        <v/>
-      </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="19" t="n"/>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="19" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>総労働時間</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="20">
+        <f>SUM(J4:J34)</f>
+        <v/>
+      </c>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="19" t="n"/>
+      <c r="H36" s="19" t="n"/>
+      <c r="I36" s="19" t="n"/>
+      <c r="J36" s="19" t="n"/>
+      <c r="K36" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+  <mergeCells count="3">
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1998,20 +2061,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="10" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="10" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2024,7 +2087,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>※ 緑色セル(始業・終業)を編集すると 休憩・労働時間・残業・深夜・合計が自動再計算されます</t>
+          <t>※ 緑色の「出社」「退社」を編集すると、通常/残業/休憩/合計が自動再計算されます</t>
         </is>
       </c>
     </row>
@@ -2041,86 +2104,87 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>始業</t>
+          <t>出社</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>終業</t>
+          <t>退社</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>残業</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
           <t>休憩</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>労働時間</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>休日労働時間</t>
-        </is>
-      </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>時間外労働時間</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>深夜労働時間</t>
+          <t>週開始</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>総労働</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>週開始(月)</t>
+          <t>深夜</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="16" t="n">
         <v>46054</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="17">
         <f>TEXT(A4,"aaa")</f>
         <v/>
       </c>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n"/>
-      <c r="E4" s="15">
-        <f>IFERROR(IF(D4-C4&gt;TIME(9,0,0),TIME(1,0,0),IF(D4-C4&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="15">
-        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,D4-C4-E4),0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="15">
-        <f>IFERROR(MIN(F4,MAX(0,SUMIFS(F$4:F4,K$4:K4,K4)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="15">
-        <f>IFERROR(IF(F4=0,0,MAX(0,MIN(D4,29/24)-MAX(C4,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="E4" s="18">
+        <f>IF(OR(WEEKDAY(A4,2)&gt;=6,J4=0),"",MIN(TIME(8,0,0),J4-F4))</f>
+        <v/>
+      </c>
+      <c r="F4" s="18">
+        <f>IFERROR(MIN(J4,MAX(0,SUMIFS(J$4:J4,I$4:I4,I4)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="18">
+        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,IF(D4-C4&gt;TIME(9,0,0),TIME(1,0,0),IF(D4-C4&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K4" s="13">
+      <c r="I4" s="16">
         <f>IFERROR(A4-WEEKDAY(A4,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="18">
+        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,D4-C4-G4),0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="18">
+        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,MAX(0,MIN(D4,29/24)-MAX(C4,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2139,27 +2203,28 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E5" s="12">
-        <f>IFERROR(IF(D5-C5&gt;TIME(9,0,0),TIME(1,0,0),IF(D5-C5&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A5,2)&gt;=6,J5=0),"",MIN(TIME(8,0,0),J5-F5))</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,D5-C5-E5),0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="12">
-        <f>IFERROR(MIN(F5,MAX(0,SUMIFS(F$4:F5,K$4:K5,K5)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I5" s="12">
-        <f>IFERROR(IF(F5=0,0,MAX(0,MIN(D5,29/24)-MAX(C5,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J5" s="11" t="inlineStr"/>
-      <c r="K5" s="10">
+        <f>IFERROR(MIN(J5,MAX(0,SUMIFS(J$4:J5,I$4:I5,I5)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="12">
+        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,IF(D5-C5&gt;TIME(9,0,0),TIME(1,0,0),IF(D5-C5&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="11" t="inlineStr"/>
+      <c r="I5" s="10">
         <f>IFERROR(A5-WEEKDAY(A5,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="12">
+        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,D5-C5-G5),0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="12">
+        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,MAX(0,MIN(D5,29/24)-MAX(C5,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2178,27 +2243,28 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E6" s="12">
-        <f>IFERROR(IF(D6-C6&gt;TIME(9,0,0),TIME(1,0,0),IF(D6-C6&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A6,2)&gt;=6,J6=0),"",MIN(TIME(8,0,0),J6-F6))</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,D6-C6-E6),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12">
-        <f>IFERROR(MIN(F6,MAX(0,SUMIFS(F$4:F6,K$4:K6,K6)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="12">
-        <f>IFERROR(IF(F6=0,0,MAX(0,MIN(D6,29/24)-MAX(C6,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J6" s="11" t="inlineStr"/>
-      <c r="K6" s="10">
+        <f>IFERROR(MIN(J6,MAX(0,SUMIFS(J$4:J6,I$4:I6,I6)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="12">
+        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,IF(D6-C6&gt;TIME(9,0,0),TIME(1,0,0),IF(D6-C6&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="11" t="inlineStr"/>
+      <c r="I6" s="10">
         <f>IFERROR(A6-WEEKDAY(A6,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="12">
+        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,D6-C6-G6),0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,MAX(0,MIN(D6,29/24)-MAX(C6,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2217,27 +2283,28 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E7" s="12">
-        <f>IFERROR(IF(D7-C7&gt;TIME(9,0,0),TIME(1,0,0),IF(D7-C7&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A7,2)&gt;=6,J7=0),"",MIN(TIME(8,0,0),J7-F7))</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,D7-C7-E7),0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12">
-        <f>IFERROR(MIN(F7,MAX(0,SUMIFS(F$4:F7,K$4:K7,K7)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="12">
-        <f>IFERROR(IF(F7=0,0,MAX(0,MIN(D7,29/24)-MAX(C7,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J7" s="11" t="inlineStr"/>
-      <c r="K7" s="10">
+        <f>IFERROR(MIN(J7,MAX(0,SUMIFS(J$4:J7,I$4:I7,I7)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,IF(D7-C7&gt;TIME(9,0,0),TIME(1,0,0),IF(D7-C7&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="11" t="inlineStr"/>
+      <c r="I7" s="10">
         <f>IFERROR(A7-WEEKDAY(A7,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,D7-C7-G7),0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="12">
+        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,MAX(0,MIN(D7,29/24)-MAX(C7,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2256,27 +2323,28 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E8" s="12">
-        <f>IFERROR(IF(D8-C8&gt;TIME(9,0,0),TIME(1,0,0),IF(D8-C8&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A8,2)&gt;=6,J8=0),"",MIN(TIME(8,0,0),J8-F8))</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,D8-C8-E8),0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12">
-        <f>IFERROR(MIN(F8,MAX(0,SUMIFS(F$4:F8,K$4:K8,K8)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="12">
-        <f>IFERROR(IF(F8=0,0,MAX(0,MIN(D8,29/24)-MAX(C8,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="11" t="inlineStr"/>
-      <c r="K8" s="10">
+        <f>IFERROR(MIN(J8,MAX(0,SUMIFS(J$4:J8,I$4:I8,I8)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,IF(D8-C8&gt;TIME(9,0,0),TIME(1,0,0),IF(D8-C8&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="11" t="inlineStr"/>
+      <c r="I8" s="10">
         <f>IFERROR(A8-WEEKDAY(A8,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,D8-C8-G8),0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,MAX(0,MIN(D8,29/24)-MAX(C8,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2295,35 +2363,36 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E9" s="12">
-        <f>IFERROR(IF(D9-C9&gt;TIME(9,0,0),TIME(1,0,0),IF(D9-C9&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A9,2)&gt;=6,J9=0),"",MIN(TIME(8,0,0),J9-F9))</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,D9-C9-E9),0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12">
-        <f>IFERROR(MIN(F9,MAX(0,SUMIFS(F$4:F9,K$4:K9,K9)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I9" s="12">
-        <f>IFERROR(IF(F9=0,0,MAX(0,MIN(D9,29/24)-MAX(C9,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J9" s="11" t="inlineStr"/>
-      <c r="K9" s="10">
+        <f>IFERROR(MIN(J9,MAX(0,SUMIFS(J$4:J9,I$4:I9,I9)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="12">
+        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,IF(D9-C9&gt;TIME(9,0,0),TIME(1,0,0),IF(D9-C9&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="11" t="inlineStr"/>
+      <c r="I9" s="10">
         <f>IFERROR(A9-WEEKDAY(A9,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J9" s="12">
+        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,D9-C9-G9),0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="12">
+        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,MAX(0,MIN(D9,29/24)-MAX(C9,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="13" t="n">
         <v>46060</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="14">
         <f>TEXT(A10,"aaa")</f>
         <v/>
       </c>
@@ -2333,67 +2402,69 @@
       <c r="D10" s="8" t="n">
         <v>0.4236111111111111</v>
       </c>
-      <c r="E10" s="12">
-        <f>IFERROR(IF(D10-C10&gt;TIME(9,0,0),TIME(1,0,0),IF(D10-C10&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
-        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,D10-C10-E10),0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12">
-        <f>IFERROR(MIN(F10,MAX(0,SUMIFS(F$4:F10,K$4:K10,K10)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I10" s="12">
-        <f>IFERROR(IF(F10=0,0,MAX(0,MIN(D10,29/24)-MAX(C10,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J10" s="11" t="inlineStr"/>
-      <c r="K10" s="10">
+      <c r="E10" s="15">
+        <f>IF(OR(WEEKDAY(A10,2)&gt;=6,J10=0),"",MIN(TIME(8,0,0),J10-F10))</f>
+        <v/>
+      </c>
+      <c r="F10" s="15">
+        <f>IFERROR(MIN(J10,MAX(0,SUMIFS(J$4:J10,I$4:I10,I10)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="15">
+        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,IF(D10-C10&gt;TIME(9,0,0),TIME(1,0,0),IF(D10-C10&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="13">
         <f>IFERROR(A10-WEEKDAY(A10,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J10" s="15">
+        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,D10-C10-G10),0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="15">
+        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,MAX(0,MIN(D10,29/24)-MAX(C10,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="16" t="n">
         <v>46061</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="17">
         <f>TEXT(A11,"aaa")</f>
         <v/>
       </c>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15">
-        <f>IFERROR(IF(D11-C11&gt;TIME(9,0,0),TIME(1,0,0),IF(D11-C11&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="15">
-        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,D11-C11-E11),0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="15">
-        <f>IFERROR(MIN(F11,MAX(0,SUMIFS(F$4:F11,K$4:K11,K11)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I11" s="15">
-        <f>IFERROR(IF(F11=0,0,MAX(0,MIN(D11,29/24)-MAX(C11,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="E11" s="18">
+        <f>IF(OR(WEEKDAY(A11,2)&gt;=6,J11=0),"",MIN(TIME(8,0,0),J11-F11))</f>
+        <v/>
+      </c>
+      <c r="F11" s="18">
+        <f>IFERROR(MIN(J11,MAX(0,SUMIFS(J$4:J11,I$4:I11,I11)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="18">
+        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,IF(D11-C11&gt;TIME(9,0,0),TIME(1,0,0),IF(D11-C11&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K11" s="13">
+      <c r="I11" s="16">
         <f>IFERROR(A11-WEEKDAY(A11,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="18">
+        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,D11-C11-G11),0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="18">
+        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,MAX(0,MIN(D11,29/24)-MAX(C11,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2412,27 +2483,28 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E12" s="12">
-        <f>IFERROR(IF(D12-C12&gt;TIME(9,0,0),TIME(1,0,0),IF(D12-C12&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A12,2)&gt;=6,J12=0),"",MIN(TIME(8,0,0),J12-F12))</f>
         <v/>
       </c>
       <c r="F12" s="12">
-        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,D12-C12-E12),0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <f>IFERROR(MIN(F12,MAX(0,SUMIFS(F$4:F12,K$4:K12,K12)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="12">
-        <f>IFERROR(IF(F12=0,0,MAX(0,MIN(D12,29/24)-MAX(C12,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
-      <c r="K12" s="10">
+        <f>IFERROR(MIN(J12,MAX(0,SUMIFS(J$4:J12,I$4:I12,I12)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="12">
+        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,IF(D12-C12&gt;TIME(9,0,0),TIME(1,0,0),IF(D12-C12&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="10">
         <f>IFERROR(A12-WEEKDAY(A12,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="12">
+        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,D12-C12-G12),0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="12">
+        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,MAX(0,MIN(D12,29/24)-MAX(C12,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2451,27 +2523,28 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E13" s="12">
-        <f>IFERROR(IF(D13-C13&gt;TIME(9,0,0),TIME(1,0,0),IF(D13-C13&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A13,2)&gt;=6,J13=0),"",MIN(TIME(8,0,0),J13-F13))</f>
         <v/>
       </c>
       <c r="F13" s="12">
-        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,D13-C13-E13),0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <f>IFERROR(MIN(F13,MAX(0,SUMIFS(F$4:F13,K$4:K13,K13)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="12">
-        <f>IFERROR(IF(F13=0,0,MAX(0,MIN(D13,29/24)-MAX(C13,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J13" s="11" t="inlineStr"/>
-      <c r="K13" s="10">
+        <f>IFERROR(MIN(J13,MAX(0,SUMIFS(J$4:J13,I$4:I13,I13)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,IF(D13-C13&gt;TIME(9,0,0),TIME(1,0,0),IF(D13-C13&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="11" t="inlineStr"/>
+      <c r="I13" s="10">
         <f>IFERROR(A13-WEEKDAY(A13,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="12">
+        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,D13-C13-G13),0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="12">
+        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,MAX(0,MIN(D13,29/24)-MAX(C13,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2490,27 +2563,28 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E14" s="12">
-        <f>IFERROR(IF(D14-C14&gt;TIME(9,0,0),TIME(1,0,0),IF(D14-C14&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A14,2)&gt;=6,J14=0),"",MIN(TIME(8,0,0),J14-F14))</f>
         <v/>
       </c>
       <c r="F14" s="12">
-        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,D14-C14-E14),0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12">
-        <f>IFERROR(MIN(F14,MAX(0,SUMIFS(F$4:F14,K$4:K14,K14)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="12">
-        <f>IFERROR(IF(F14=0,0,MAX(0,MIN(D14,29/24)-MAX(C14,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
-      <c r="K14" s="10">
+        <f>IFERROR(MIN(J14,MAX(0,SUMIFS(J$4:J14,I$4:I14,I14)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="12">
+        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,IF(D14-C14&gt;TIME(9,0,0),TIME(1,0,0),IF(D14-C14&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="11" t="inlineStr"/>
+      <c r="I14" s="10">
         <f>IFERROR(A14-WEEKDAY(A14,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="12">
+        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,D14-C14-G14),0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="12">
+        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,MAX(0,MIN(D14,29/24)-MAX(C14,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2529,27 +2603,28 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E15" s="12">
-        <f>IFERROR(IF(D15-C15&gt;TIME(9,0,0),TIME(1,0,0),IF(D15-C15&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A15,2)&gt;=6,J15=0),"",MIN(TIME(8,0,0),J15-F15))</f>
         <v/>
       </c>
       <c r="F15" s="12">
-        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,D15-C15-E15),0)</f>
-        <v/>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="12">
-        <f>IFERROR(MIN(F15,MAX(0,SUMIFS(F$4:F15,K$4:K15,K15)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I15" s="12">
-        <f>IFERROR(IF(F15=0,0,MAX(0,MIN(D15,29/24)-MAX(C15,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="10">
+        <f>IFERROR(MIN(J15,MAX(0,SUMIFS(J$4:J15,I$4:I15,I15)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="12">
+        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,IF(D15-C15&gt;TIME(9,0,0),TIME(1,0,0),IF(D15-C15&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="10">
         <f>IFERROR(A15-WEEKDAY(A15,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="12">
+        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,D15-C15-G15),0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="12">
+        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,MAX(0,MIN(D15,29/24)-MAX(C15,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2568,35 +2643,36 @@
         <v>0.4236111111111111</v>
       </c>
       <c r="E16" s="12">
-        <f>IFERROR(IF(D16-C16&gt;TIME(9,0,0),TIME(1,0,0),IF(D16-C16&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A16,2)&gt;=6,J16=0),"",MIN(TIME(8,0,0),J16-F16))</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,D16-C16-E16),0)</f>
-        <v/>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="12">
-        <f>IFERROR(MIN(F16,MAX(0,SUMIFS(F$4:F16,K$4:K16,K16)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="12">
-        <f>IFERROR(IF(F16=0,0,MAX(0,MIN(D16,29/24)-MAX(C16,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J16" s="11" t="inlineStr"/>
-      <c r="K16" s="10">
+        <f>IFERROR(MIN(J16,MAX(0,SUMIFS(J$4:J16,I$4:I16,I16)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="12">
+        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,IF(D16-C16&gt;TIME(9,0,0),TIME(1,0,0),IF(D16-C16&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="11" t="inlineStr"/>
+      <c r="I16" s="10">
         <f>IFERROR(A16-WEEKDAY(A16,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J16" s="12">
+        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,D16-C16-G16),0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="12">
+        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,MAX(0,MIN(D16,29/24)-MAX(C16,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="13" t="n">
         <v>46067</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="14">
         <f>TEXT(A17,"aaa")</f>
         <v/>
       </c>
@@ -2606,67 +2682,69 @@
       <c r="D17" s="8" t="n">
         <v>0.4236111111111111</v>
       </c>
-      <c r="E17" s="12">
-        <f>IFERROR(IF(D17-C17&gt;TIME(9,0,0),TIME(1,0,0),IF(D17-C17&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
-        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,D17-C17-E17),0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="12">
-        <f>IFERROR(MIN(F17,MAX(0,SUMIFS(F$4:F17,K$4:K17,K17)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="12">
-        <f>IFERROR(IF(F17=0,0,MAX(0,MIN(D17,29/24)-MAX(C17,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J17" s="11" t="inlineStr"/>
-      <c r="K17" s="10">
+      <c r="E17" s="15">
+        <f>IF(OR(WEEKDAY(A17,2)&gt;=6,J17=0),"",MIN(TIME(8,0,0),J17-F17))</f>
+        <v/>
+      </c>
+      <c r="F17" s="15">
+        <f>IFERROR(MIN(J17,MAX(0,SUMIFS(J$4:J17,I$4:I17,I17)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="15">
+        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,IF(D17-C17&gt;TIME(9,0,0),TIME(1,0,0),IF(D17-C17&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="13">
         <f>IFERROR(A17-WEEKDAY(A17,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J17" s="15">
+        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,D17-C17-G17),0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="15">
+        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,MAX(0,MIN(D17,29/24)-MAX(C17,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n">
+      <c r="A18" s="16" t="n">
         <v>46068</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="17">
         <f>TEXT(A18,"aaa")</f>
         <v/>
       </c>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
-      <c r="E18" s="15">
-        <f>IFERROR(IF(D18-C18&gt;TIME(9,0,0),TIME(1,0,0),IF(D18-C18&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="15">
-        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,D18-C18-E18),0)</f>
-        <v/>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="15">
-        <f>IFERROR(MIN(F18,MAX(0,SUMIFS(F$4:F18,K$4:K18,K18)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I18" s="15">
-        <f>IFERROR(IF(F18=0,0,MAX(0,MIN(D18,29/24)-MAX(C18,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="E18" s="18">
+        <f>IF(OR(WEEKDAY(A18,2)&gt;=6,J18=0),"",MIN(TIME(8,0,0),J18-F18))</f>
+        <v/>
+      </c>
+      <c r="F18" s="18">
+        <f>IFERROR(MIN(J18,MAX(0,SUMIFS(J$4:J18,I$4:I18,I18)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="18">
+        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,IF(D18-C18&gt;TIME(9,0,0),TIME(1,0,0),IF(D18-C18&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K18" s="13">
+      <c r="I18" s="16">
         <f>IFERROR(A18-WEEKDAY(A18,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="18">
+        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,D18-C18-G18),0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="18">
+        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,MAX(0,MIN(D18,29/24)-MAX(C18,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2685,27 +2763,28 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="E19" s="12">
-        <f>IFERROR(IF(D19-C19&gt;TIME(9,0,0),TIME(1,0,0),IF(D19-C19&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A19,2)&gt;=6,J19=0),"",MIN(TIME(8,0,0),J19-F19))</f>
         <v/>
       </c>
       <c r="F19" s="12">
-        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,D19-C19-E19),0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12">
-        <f>IFERROR(MIN(F19,MAX(0,SUMIFS(F$4:F19,K$4:K19,K19)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I19" s="12">
-        <f>IFERROR(IF(F19=0,0,MAX(0,MIN(D19,29/24)-MAX(C19,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="11" t="inlineStr"/>
-      <c r="K19" s="10">
+        <f>IFERROR(MIN(J19,MAX(0,SUMIFS(J$4:J19,I$4:I19,I19)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="12">
+        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,IF(D19-C19&gt;TIME(9,0,0),TIME(1,0,0),IF(D19-C19&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="10">
         <f>IFERROR(A19-WEEKDAY(A19,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="12">
+        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,D19-C19-G19),0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="12">
+        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,MAX(0,MIN(D19,29/24)-MAX(C19,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2724,27 +2803,28 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="E20" s="12">
-        <f>IFERROR(IF(D20-C20&gt;TIME(9,0,0),TIME(1,0,0),IF(D20-C20&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A20,2)&gt;=6,J20=0),"",MIN(TIME(8,0,0),J20-F20))</f>
         <v/>
       </c>
       <c r="F20" s="12">
-        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,D20-C20-E20),0)</f>
-        <v/>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="12">
-        <f>IFERROR(MIN(F20,MAX(0,SUMIFS(F$4:F20,K$4:K20,K20)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I20" s="12">
-        <f>IFERROR(IF(F20=0,0,MAX(0,MIN(D20,29/24)-MAX(C20,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="10">
+        <f>IFERROR(MIN(J20,MAX(0,SUMIFS(J$4:J20,I$4:I20,I20)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="12">
+        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,IF(D20-C20&gt;TIME(9,0,0),TIME(1,0,0),IF(D20-C20&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="11" t="inlineStr"/>
+      <c r="I20" s="10">
         <f>IFERROR(A20-WEEKDAY(A20,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="12">
+        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,D20-C20-G20),0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="12">
+        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,MAX(0,MIN(D20,29/24)-MAX(C20,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2763,27 +2843,28 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="E21" s="12">
-        <f>IFERROR(IF(D21-C21&gt;TIME(9,0,0),TIME(1,0,0),IF(D21-C21&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A21,2)&gt;=6,J21=0),"",MIN(TIME(8,0,0),J21-F21))</f>
         <v/>
       </c>
       <c r="F21" s="12">
-        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,D21-C21-E21),0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="12">
-        <f>IFERROR(MIN(F21,MAX(0,SUMIFS(F$4:F21,K$4:K21,K21)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="12">
-        <f>IFERROR(IF(F21=0,0,MAX(0,MIN(D21,29/24)-MAX(C21,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="10">
+        <f>IFERROR(MIN(J21,MAX(0,SUMIFS(J$4:J21,I$4:I21,I21)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="12">
+        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,IF(D21-C21&gt;TIME(9,0,0),TIME(1,0,0),IF(D21-C21&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="11" t="inlineStr"/>
+      <c r="I21" s="10">
         <f>IFERROR(A21-WEEKDAY(A21,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="12">
+        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,D21-C21-G21),0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="12">
+        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,MAX(0,MIN(D21,29/24)-MAX(C21,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2802,27 +2883,28 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="E22" s="12">
-        <f>IFERROR(IF(D22-C22&gt;TIME(9,0,0),TIME(1,0,0),IF(D22-C22&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A22,2)&gt;=6,J22=0),"",MIN(TIME(8,0,0),J22-F22))</f>
         <v/>
       </c>
       <c r="F22" s="12">
-        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,D22-C22-E22),0)</f>
-        <v/>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="12">
-        <f>IFERROR(MIN(F22,MAX(0,SUMIFS(F$4:F22,K$4:K22,K22)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="12">
-        <f>IFERROR(IF(F22=0,0,MAX(0,MIN(D22,29/24)-MAX(C22,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="11" t="inlineStr"/>
-      <c r="K22" s="10">
+        <f>IFERROR(MIN(J22,MAX(0,SUMIFS(J$4:J22,I$4:I22,I22)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="12">
+        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,IF(D22-C22&gt;TIME(9,0,0),TIME(1,0,0),IF(D22-C22&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="11" t="inlineStr"/>
+      <c r="I22" s="10">
         <f>IFERROR(A22-WEEKDAY(A22,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,D22-C22-G22),0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="12">
+        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,MAX(0,MIN(D22,29/24)-MAX(C22,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2841,35 +2923,36 @@
         <v>0.6805555555555556</v>
       </c>
       <c r="E23" s="12">
-        <f>IFERROR(IF(D23-C23&gt;TIME(9,0,0),TIME(1,0,0),IF(D23-C23&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A23,2)&gt;=6,J23=0),"",MIN(TIME(8,0,0),J23-F23))</f>
         <v/>
       </c>
       <c r="F23" s="12">
-        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,D23-C23-E23),0)</f>
-        <v/>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="12">
-        <f>IFERROR(MIN(F23,MAX(0,SUMIFS(F$4:F23,K$4:K23,K23)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I23" s="12">
-        <f>IFERROR(IF(F23=0,0,MAX(0,MIN(D23,29/24)-MAX(C23,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="10">
+        <f>IFERROR(MIN(J23,MAX(0,SUMIFS(J$4:J23,I$4:I23,I23)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="12">
+        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,IF(D23-C23&gt;TIME(9,0,0),TIME(1,0,0),IF(D23-C23&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="11" t="inlineStr"/>
+      <c r="I23" s="10">
         <f>IFERROR(A23-WEEKDAY(A23,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J23" s="12">
+        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,D23-C23-G23),0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="12">
+        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,MAX(0,MIN(D23,29/24)-MAX(C23,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="13" t="n">
         <v>46074</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="14">
         <f>TEXT(A24,"aaa")</f>
         <v/>
       </c>
@@ -2879,67 +2962,69 @@
       <c r="D24" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
-      <c r="E24" s="12">
-        <f>IFERROR(IF(D24-C24&gt;TIME(9,0,0),TIME(1,0,0),IF(D24-C24&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F24" s="12">
-        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,D24-C24-E24),0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="12">
-        <f>IFERROR(MIN(F24,MAX(0,SUMIFS(F$4:F24,K$4:K24,K24)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I24" s="12">
-        <f>IFERROR(IF(F24=0,0,MAX(0,MIN(D24,29/24)-MAX(C24,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="10">
+      <c r="E24" s="15">
+        <f>IF(OR(WEEKDAY(A24,2)&gt;=6,J24=0),"",MIN(TIME(8,0,0),J24-F24))</f>
+        <v/>
+      </c>
+      <c r="F24" s="15">
+        <f>IFERROR(MIN(J24,MAX(0,SUMIFS(J$4:J24,I$4:I24,I24)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="15">
+        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,IF(D24-C24&gt;TIME(9,0,0),TIME(1,0,0),IF(D24-C24&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="14" t="inlineStr"/>
+      <c r="I24" s="13">
         <f>IFERROR(A24-WEEKDAY(A24,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J24" s="15">
+        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,D24-C24-G24),0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="15">
+        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,MAX(0,MIN(D24,29/24)-MAX(C24,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="n">
+      <c r="A25" s="16" t="n">
         <v>46075</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="17">
         <f>TEXT(A25,"aaa")</f>
         <v/>
       </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
-      <c r="E25" s="15">
-        <f>IFERROR(IF(D25-C25&gt;TIME(9,0,0),TIME(1,0,0),IF(D25-C25&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F25" s="15">
-        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,D25-C25-E25),0)</f>
-        <v/>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="15">
-        <f>IFERROR(MIN(F25,MAX(0,SUMIFS(F$4:F25,K$4:K25,K25)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I25" s="15">
-        <f>IFERROR(IF(F25=0,0,MAX(0,MIN(D25,29/24)-MAX(C25,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="E25" s="18">
+        <f>IF(OR(WEEKDAY(A25,2)&gt;=6,J25=0),"",MIN(TIME(8,0,0),J25-F25))</f>
+        <v/>
+      </c>
+      <c r="F25" s="18">
+        <f>IFERROR(MIN(J25,MAX(0,SUMIFS(J$4:J25,I$4:I25,I25)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="18">
+        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,IF(D25-C25&gt;TIME(9,0,0),TIME(1,0,0),IF(D25-C25&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K25" s="13">
+      <c r="I25" s="16">
         <f>IFERROR(A25-WEEKDAY(A25,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="18">
+        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,D25-C25-G25),0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="18">
+        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,MAX(0,MIN(D25,29/24)-MAX(C25,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2958,27 +3043,28 @@
         <v>1</v>
       </c>
       <c r="E26" s="12">
-        <f>IFERROR(IF(D26-C26&gt;TIME(9,0,0),TIME(1,0,0),IF(D26-C26&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A26,2)&gt;=6,J26=0),"",MIN(TIME(8,0,0),J26-F26))</f>
         <v/>
       </c>
       <c r="F26" s="12">
-        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,D26-C26-E26),0)</f>
-        <v/>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="12">
-        <f>IFERROR(MIN(F26,MAX(0,SUMIFS(F$4:F26,K$4:K26,K26)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I26" s="12">
-        <f>IFERROR(IF(F26=0,0,MAX(0,MIN(D26,29/24)-MAX(C26,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J26" s="11" t="inlineStr"/>
-      <c r="K26" s="10">
+        <f>IFERROR(MIN(J26,MAX(0,SUMIFS(J$4:J26,I$4:I26,I26)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="12">
+        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,IF(D26-C26&gt;TIME(9,0,0),TIME(1,0,0),IF(D26-C26&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="11" t="inlineStr"/>
+      <c r="I26" s="10">
         <f>IFERROR(A26-WEEKDAY(A26,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="12">
+        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,D26-C26-G26),0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="12">
+        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,MAX(0,MIN(D26,29/24)-MAX(C26,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -2997,27 +3083,28 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E27" s="12">
-        <f>IFERROR(IF(D27-C27&gt;TIME(9,0,0),TIME(1,0,0),IF(D27-C27&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A27,2)&gt;=6,J27=0),"",MIN(TIME(8,0,0),J27-F27))</f>
         <v/>
       </c>
       <c r="F27" s="12">
-        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,D27-C27-E27),0)</f>
-        <v/>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="12">
-        <f>IFERROR(MIN(F27,MAX(0,SUMIFS(F$4:F27,K$4:K27,K27)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I27" s="12">
-        <f>IFERROR(IF(F27=0,0,MAX(0,MIN(D27,29/24)-MAX(C27,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
-      <c r="K27" s="10">
+        <f>IFERROR(MIN(J27,MAX(0,SUMIFS(J$4:J27,I$4:I27,I27)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="12">
+        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,IF(D27-C27&gt;TIME(9,0,0),TIME(1,0,0),IF(D27-C27&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="11" t="inlineStr"/>
+      <c r="I27" s="10">
         <f>IFERROR(A27-WEEKDAY(A27,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="12">
+        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,D27-C27-G27),0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="12">
+        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,MAX(0,MIN(D27,29/24)-MAX(C27,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3036,27 +3123,28 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E28" s="12">
-        <f>IFERROR(IF(D28-C28&gt;TIME(9,0,0),TIME(1,0,0),IF(D28-C28&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A28,2)&gt;=6,J28=0),"",MIN(TIME(8,0,0),J28-F28))</f>
         <v/>
       </c>
       <c r="F28" s="12">
-        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,D28-C28-E28),0)</f>
-        <v/>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="12">
-        <f>IFERROR(MIN(F28,MAX(0,SUMIFS(F$4:F28,K$4:K28,K28)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I28" s="12">
-        <f>IFERROR(IF(F28=0,0,MAX(0,MIN(D28,29/24)-MAX(C28,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J28" s="11" t="inlineStr"/>
-      <c r="K28" s="10">
+        <f>IFERROR(MIN(J28,MAX(0,SUMIFS(J$4:J28,I$4:I28,I28)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="12">
+        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,IF(D28-C28&gt;TIME(9,0,0),TIME(1,0,0),IF(D28-C28&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="11" t="inlineStr"/>
+      <c r="I28" s="10">
         <f>IFERROR(A28-WEEKDAY(A28,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="12">
+        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,D28-C28-G28),0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="12">
+        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,MAX(0,MIN(D28,29/24)-MAX(C28,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3075,27 +3163,28 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E29" s="12">
-        <f>IFERROR(IF(D29-C29&gt;TIME(9,0,0),TIME(1,0,0),IF(D29-C29&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A29,2)&gt;=6,J29=0),"",MIN(TIME(8,0,0),J29-F29))</f>
         <v/>
       </c>
       <c r="F29" s="12">
-        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,D29-C29-E29),0)</f>
-        <v/>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="12">
-        <f>IFERROR(MIN(F29,MAX(0,SUMIFS(F$4:F29,K$4:K29,K29)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I29" s="12">
-        <f>IFERROR(IF(F29=0,0,MAX(0,MIN(D29,29/24)-MAX(C29,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J29" s="11" t="inlineStr"/>
-      <c r="K29" s="10">
+        <f>IFERROR(MIN(J29,MAX(0,SUMIFS(J$4:J29,I$4:I29,I29)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="12">
+        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,IF(D29-C29&gt;TIME(9,0,0),TIME(1,0,0),IF(D29-C29&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="11" t="inlineStr"/>
+      <c r="I29" s="10">
         <f>IFERROR(A29-WEEKDAY(A29,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="12">
+        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,D29-C29-G29),0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="12">
+        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,MAX(0,MIN(D29,29/24)-MAX(C29,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3114,35 +3203,36 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E30" s="12">
-        <f>IFERROR(IF(D30-C30&gt;TIME(9,0,0),TIME(1,0,0),IF(D30-C30&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A30,2)&gt;=6,J30=0),"",MIN(TIME(8,0,0),J30-F30))</f>
         <v/>
       </c>
       <c r="F30" s="12">
-        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,D30-C30-E30),0)</f>
-        <v/>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="12">
-        <f>IFERROR(MIN(F30,MAX(0,SUMIFS(F$4:F30,K$4:K30,K30)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I30" s="12">
-        <f>IFERROR(IF(F30=0,0,MAX(0,MIN(D30,29/24)-MAX(C30,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J30" s="11" t="inlineStr"/>
-      <c r="K30" s="10">
+        <f>IFERROR(MIN(J30,MAX(0,SUMIFS(J$4:J30,I$4:I30,I30)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="12">
+        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,IF(D30-C30&gt;TIME(9,0,0),TIME(1,0,0),IF(D30-C30&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="11" t="inlineStr"/>
+      <c r="I30" s="10">
         <f>IFERROR(A30-WEEKDAY(A30,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J30" s="12">
+        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,D30-C30-G30),0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="12">
+        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,MAX(0,MIN(D30,29/24)-MAX(C30,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="13" t="n">
         <v>46081</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="14">
         <f>TEXT(A31,"aaa")</f>
         <v/>
       </c>
@@ -3152,67 +3242,86 @@
       <c r="D31" s="8" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="E31" s="12">
-        <f>IFERROR(IF(D31-C31&gt;TIME(9,0,0),TIME(1,0,0),IF(D31-C31&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F31" s="12">
-        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,D31-C31-E31),0)</f>
-        <v/>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="12">
-        <f>IFERROR(MIN(F31,MAX(0,SUMIFS(F$4:F31,K$4:K31,K31)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I31" s="12">
-        <f>IFERROR(IF(F31=0,0,MAX(0,MIN(D31,29/24)-MAX(C31,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J31" s="11" t="inlineStr"/>
-      <c r="K31" s="10">
+      <c r="E31" s="15">
+        <f>IF(OR(WEEKDAY(A31,2)&gt;=6,J31=0),"",MIN(TIME(8,0,0),J31-F31))</f>
+        <v/>
+      </c>
+      <c r="F31" s="15">
+        <f>IFERROR(MIN(J31,MAX(0,SUMIFS(J$4:J31,I$4:I31,I31)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="15">
+        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,IF(D31-C31&gt;TIME(9,0,0),TIME(1,0,0),IF(D31-C31&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="14" t="inlineStr"/>
+      <c r="I31" s="13">
         <f>IFERROR(A31-WEEKDAY(A31,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J31" s="15">
+        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,D31-C31-G31),0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="15">
+        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,MAX(0,MIN(D31,29/24)-MAX(C31,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B32" s="16">
-        <f>COUNTIF(F4:F31,"&gt;0")&amp;"日"</f>
-        <v/>
-      </c>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="17">
+      <c r="B32" s="19">
+        <f>COUNTIF(J4:J31,"&gt;0")&amp;"日"</f>
+        <v/>
+      </c>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="20">
+        <f>SUM(E4:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="20">
         <f>SUM(F4:F31)</f>
         <v/>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="20">
         <f>SUM(G4:G31)</f>
         <v/>
       </c>
-      <c r="H32" s="17">
-        <f>SUM(H4:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="17">
-        <f>SUM(I4:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
+      <c r="H32" s="19" t="n"/>
+      <c r="I32" s="19" t="n"/>
+      <c r="J32" s="19" t="n"/>
+      <c r="K32" s="19" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>総労働時間</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="20">
+        <f>SUM(J4:J31)</f>
+        <v/>
+      </c>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="19" t="n"/>
+      <c r="J33" s="19" t="n"/>
+      <c r="K33" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3224,20 +3333,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="10" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="10" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3250,7 +3359,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>※ 緑色セル(始業・終業)を編集すると 休憩・労働時間・残業・深夜・合計が自動再計算されます</t>
+          <t>※ 緑色の「出社」「退社」を編集すると、通常/残業/休憩/合計が自動再計算されます</t>
         </is>
       </c>
     </row>
@@ -3267,86 +3376,87 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>始業</t>
+          <t>出社</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>終業</t>
+          <t>退社</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>残業</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
           <t>休憩</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>労働時間</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>休日労働時間</t>
-        </is>
-      </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>時間外労働時間</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>深夜労働時間</t>
+          <t>週開始</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>総労働</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>週開始(月)</t>
+          <t>深夜</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="16" t="n">
         <v>46082</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="17">
         <f>TEXT(A4,"aaa")</f>
         <v/>
       </c>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n"/>
-      <c r="E4" s="15">
-        <f>IFERROR(IF(D4-C4&gt;TIME(9,0,0),TIME(1,0,0),IF(D4-C4&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="15">
-        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,D4-C4-E4),0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="15">
-        <f>IFERROR(MIN(F4,MAX(0,SUMIFS(F$4:F4,K$4:K4,K4)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="15">
-        <f>IFERROR(IF(F4=0,0,MAX(0,MIN(D4,29/24)-MAX(C4,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="E4" s="18">
+        <f>IF(OR(WEEKDAY(A4,2)&gt;=6,J4=0),"",MIN(TIME(8,0,0),J4-F4))</f>
+        <v/>
+      </c>
+      <c r="F4" s="18">
+        <f>IFERROR(MIN(J4,MAX(0,SUMIFS(J$4:J4,I$4:I4,I4)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="18">
+        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,IF(D4-C4&gt;TIME(9,0,0),TIME(1,0,0),IF(D4-C4&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K4" s="13">
+      <c r="I4" s="16">
         <f>IFERROR(A4-WEEKDAY(A4,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="18">
+        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,D4-C4-G4),0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="18">
+        <f>IFERROR(IF(OR(C4="",D4="",D4&lt;=C4),0,MAX(0,MIN(D4,29/24)-MAX(C4,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3365,27 +3475,28 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E5" s="12">
-        <f>IFERROR(IF(D5-C5&gt;TIME(9,0,0),TIME(1,0,0),IF(D5-C5&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A5,2)&gt;=6,J5=0),"",MIN(TIME(8,0,0),J5-F5))</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,D5-C5-E5),0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="12">
-        <f>IFERROR(MIN(F5,MAX(0,SUMIFS(F$4:F5,K$4:K5,K5)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I5" s="12">
-        <f>IFERROR(IF(F5=0,0,MAX(0,MIN(D5,29/24)-MAX(C5,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J5" s="11" t="inlineStr"/>
-      <c r="K5" s="10">
+        <f>IFERROR(MIN(J5,MAX(0,SUMIFS(J$4:J5,I$4:I5,I5)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="12">
+        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,IF(D5-C5&gt;TIME(9,0,0),TIME(1,0,0),IF(D5-C5&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="11" t="inlineStr"/>
+      <c r="I5" s="10">
         <f>IFERROR(A5-WEEKDAY(A5,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="12">
+        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,D5-C5-G5),0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="12">
+        <f>IFERROR(IF(OR(C5="",D5="",D5&lt;=C5),0,MAX(0,MIN(D5,29/24)-MAX(C5,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3404,27 +3515,28 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E6" s="12">
-        <f>IFERROR(IF(D6-C6&gt;TIME(9,0,0),TIME(1,0,0),IF(D6-C6&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A6,2)&gt;=6,J6=0),"",MIN(TIME(8,0,0),J6-F6))</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,D6-C6-E6),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12">
-        <f>IFERROR(MIN(F6,MAX(0,SUMIFS(F$4:F6,K$4:K6,K6)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="12">
-        <f>IFERROR(IF(F6=0,0,MAX(0,MIN(D6,29/24)-MAX(C6,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J6" s="11" t="inlineStr"/>
-      <c r="K6" s="10">
+        <f>IFERROR(MIN(J6,MAX(0,SUMIFS(J$4:J6,I$4:I6,I6)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="12">
+        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,IF(D6-C6&gt;TIME(9,0,0),TIME(1,0,0),IF(D6-C6&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="11" t="inlineStr"/>
+      <c r="I6" s="10">
         <f>IFERROR(A6-WEEKDAY(A6,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="12">
+        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,D6-C6-G6),0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>IFERROR(IF(OR(C6="",D6="",D6&lt;=C6),0,MAX(0,MIN(D6,29/24)-MAX(C6,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3443,27 +3555,28 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E7" s="12">
-        <f>IFERROR(IF(D7-C7&gt;TIME(9,0,0),TIME(1,0,0),IF(D7-C7&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A7,2)&gt;=6,J7=0),"",MIN(TIME(8,0,0),J7-F7))</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,D7-C7-E7),0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12">
-        <f>IFERROR(MIN(F7,MAX(0,SUMIFS(F$4:F7,K$4:K7,K7)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="12">
-        <f>IFERROR(IF(F7=0,0,MAX(0,MIN(D7,29/24)-MAX(C7,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J7" s="11" t="inlineStr"/>
-      <c r="K7" s="10">
+        <f>IFERROR(MIN(J7,MAX(0,SUMIFS(J$4:J7,I$4:I7,I7)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,IF(D7-C7&gt;TIME(9,0,0),TIME(1,0,0),IF(D7-C7&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="11" t="inlineStr"/>
+      <c r="I7" s="10">
         <f>IFERROR(A7-WEEKDAY(A7,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,D7-C7-G7),0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="12">
+        <f>IFERROR(IF(OR(C7="",D7="",D7&lt;=C7),0,MAX(0,MIN(D7,29/24)-MAX(C7,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3482,27 +3595,28 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E8" s="12">
-        <f>IFERROR(IF(D8-C8&gt;TIME(9,0,0),TIME(1,0,0),IF(D8-C8&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A8,2)&gt;=6,J8=0),"",MIN(TIME(8,0,0),J8-F8))</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,D8-C8-E8),0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12">
-        <f>IFERROR(MIN(F8,MAX(0,SUMIFS(F$4:F8,K$4:K8,K8)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="12">
-        <f>IFERROR(IF(F8=0,0,MAX(0,MIN(D8,29/24)-MAX(C8,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="11" t="inlineStr"/>
-      <c r="K8" s="10">
+        <f>IFERROR(MIN(J8,MAX(0,SUMIFS(J$4:J8,I$4:I8,I8)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,IF(D8-C8&gt;TIME(9,0,0),TIME(1,0,0),IF(D8-C8&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="11" t="inlineStr"/>
+      <c r="I8" s="10">
         <f>IFERROR(A8-WEEKDAY(A8,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,D8-C8-G8),0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>IFERROR(IF(OR(C8="",D8="",D8&lt;=C8),0,MAX(0,MIN(D8,29/24)-MAX(C8,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3521,35 +3635,36 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E9" s="12">
-        <f>IFERROR(IF(D9-C9&gt;TIME(9,0,0),TIME(1,0,0),IF(D9-C9&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A9,2)&gt;=6,J9=0),"",MIN(TIME(8,0,0),J9-F9))</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,D9-C9-E9),0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12">
-        <f>IFERROR(MIN(F9,MAX(0,SUMIFS(F$4:F9,K$4:K9,K9)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I9" s="12">
-        <f>IFERROR(IF(F9=0,0,MAX(0,MIN(D9,29/24)-MAX(C9,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J9" s="11" t="inlineStr"/>
-      <c r="K9" s="10">
+        <f>IFERROR(MIN(J9,MAX(0,SUMIFS(J$4:J9,I$4:I9,I9)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="12">
+        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,IF(D9-C9&gt;TIME(9,0,0),TIME(1,0,0),IF(D9-C9&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="11" t="inlineStr"/>
+      <c r="I9" s="10">
         <f>IFERROR(A9-WEEKDAY(A9,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J9" s="12">
+        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,D9-C9-G9),0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="12">
+        <f>IFERROR(IF(OR(C9="",D9="",D9&lt;=C9),0,MAX(0,MIN(D9,29/24)-MAX(C9,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="13" t="n">
         <v>46088</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="14">
         <f>TEXT(A10,"aaa")</f>
         <v/>
       </c>
@@ -3559,67 +3674,69 @@
       <c r="D10" s="8" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="E10" s="12">
-        <f>IFERROR(IF(D10-C10&gt;TIME(9,0,0),TIME(1,0,0),IF(D10-C10&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
-        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,D10-C10-E10),0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12">
-        <f>IFERROR(MIN(F10,MAX(0,SUMIFS(F$4:F10,K$4:K10,K10)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I10" s="12">
-        <f>IFERROR(IF(F10=0,0,MAX(0,MIN(D10,29/24)-MAX(C10,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J10" s="11" t="inlineStr"/>
-      <c r="K10" s="10">
+      <c r="E10" s="15">
+        <f>IF(OR(WEEKDAY(A10,2)&gt;=6,J10=0),"",MIN(TIME(8,0,0),J10-F10))</f>
+        <v/>
+      </c>
+      <c r="F10" s="15">
+        <f>IFERROR(MIN(J10,MAX(0,SUMIFS(J$4:J10,I$4:I10,I10)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="15">
+        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,IF(D10-C10&gt;TIME(9,0,0),TIME(1,0,0),IF(D10-C10&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="13">
         <f>IFERROR(A10-WEEKDAY(A10,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J10" s="15">
+        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,D10-C10-G10),0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="15">
+        <f>IFERROR(IF(OR(C10="",D10="",D10&lt;=C10),0,MAX(0,MIN(D10,29/24)-MAX(C10,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="16" t="n">
         <v>46089</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="17">
         <f>TEXT(A11,"aaa")</f>
         <v/>
       </c>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15">
-        <f>IFERROR(IF(D11-C11&gt;TIME(9,0,0),TIME(1,0,0),IF(D11-C11&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="15">
-        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,D11-C11-E11),0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="15">
-        <f>IFERROR(MIN(F11,MAX(0,SUMIFS(F$4:F11,K$4:K11,K11)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I11" s="15">
-        <f>IFERROR(IF(F11=0,0,MAX(0,MIN(D11,29/24)-MAX(C11,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="E11" s="18">
+        <f>IF(OR(WEEKDAY(A11,2)&gt;=6,J11=0),"",MIN(TIME(8,0,0),J11-F11))</f>
+        <v/>
+      </c>
+      <c r="F11" s="18">
+        <f>IFERROR(MIN(J11,MAX(0,SUMIFS(J$4:J11,I$4:I11,I11)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="18">
+        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,IF(D11-C11&gt;TIME(9,0,0),TIME(1,0,0),IF(D11-C11&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K11" s="13">
+      <c r="I11" s="16">
         <f>IFERROR(A11-WEEKDAY(A11,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="18">
+        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,D11-C11-G11),0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="18">
+        <f>IFERROR(IF(OR(C11="",D11="",D11&lt;=C11),0,MAX(0,MIN(D11,29/24)-MAX(C11,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3638,27 +3755,28 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="E12" s="12">
-        <f>IFERROR(IF(D12-C12&gt;TIME(9,0,0),TIME(1,0,0),IF(D12-C12&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A12,2)&gt;=6,J12=0),"",MIN(TIME(8,0,0),J12-F12))</f>
         <v/>
       </c>
       <c r="F12" s="12">
-        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,D12-C12-E12),0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12">
-        <f>IFERROR(MIN(F12,MAX(0,SUMIFS(F$4:F12,K$4:K12,K12)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="12">
-        <f>IFERROR(IF(F12=0,0,MAX(0,MIN(D12,29/24)-MAX(C12,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
-      <c r="K12" s="10">
+        <f>IFERROR(MIN(J12,MAX(0,SUMIFS(J$4:J12,I$4:I12,I12)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="12">
+        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,IF(D12-C12&gt;TIME(9,0,0),TIME(1,0,0),IF(D12-C12&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="10">
         <f>IFERROR(A12-WEEKDAY(A12,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="12">
+        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,D12-C12-G12),0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="12">
+        <f>IFERROR(IF(OR(C12="",D12="",D12&lt;=C12),0,MAX(0,MIN(D12,29/24)-MAX(C12,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3677,27 +3795,28 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="E13" s="12">
-        <f>IFERROR(IF(D13-C13&gt;TIME(9,0,0),TIME(1,0,0),IF(D13-C13&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A13,2)&gt;=6,J13=0),"",MIN(TIME(8,0,0),J13-F13))</f>
         <v/>
       </c>
       <c r="F13" s="12">
-        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,D13-C13-E13),0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12">
-        <f>IFERROR(MIN(F13,MAX(0,SUMIFS(F$4:F13,K$4:K13,K13)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="12">
-        <f>IFERROR(IF(F13=0,0,MAX(0,MIN(D13,29/24)-MAX(C13,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J13" s="11" t="inlineStr"/>
-      <c r="K13" s="10">
+        <f>IFERROR(MIN(J13,MAX(0,SUMIFS(J$4:J13,I$4:I13,I13)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="12">
+        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,IF(D13-C13&gt;TIME(9,0,0),TIME(1,0,0),IF(D13-C13&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="11" t="inlineStr"/>
+      <c r="I13" s="10">
         <f>IFERROR(A13-WEEKDAY(A13,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="12">
+        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,D13-C13-G13),0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="12">
+        <f>IFERROR(IF(OR(C13="",D13="",D13&lt;=C13),0,MAX(0,MIN(D13,29/24)-MAX(C13,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3716,27 +3835,28 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="E14" s="12">
-        <f>IFERROR(IF(D14-C14&gt;TIME(9,0,0),TIME(1,0,0),IF(D14-C14&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A14,2)&gt;=6,J14=0),"",MIN(TIME(8,0,0),J14-F14))</f>
         <v/>
       </c>
       <c r="F14" s="12">
-        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,D14-C14-E14),0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12">
-        <f>IFERROR(MIN(F14,MAX(0,SUMIFS(F$4:F14,K$4:K14,K14)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="12">
-        <f>IFERROR(IF(F14=0,0,MAX(0,MIN(D14,29/24)-MAX(C14,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
-      <c r="K14" s="10">
+        <f>IFERROR(MIN(J14,MAX(0,SUMIFS(J$4:J14,I$4:I14,I14)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="12">
+        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,IF(D14-C14&gt;TIME(9,0,0),TIME(1,0,0),IF(D14-C14&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="11" t="inlineStr"/>
+      <c r="I14" s="10">
         <f>IFERROR(A14-WEEKDAY(A14,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="12">
+        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,D14-C14-G14),0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="12">
+        <f>IFERROR(IF(OR(C14="",D14="",D14&lt;=C14),0,MAX(0,MIN(D14,29/24)-MAX(C14,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3755,27 +3875,28 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="E15" s="12">
-        <f>IFERROR(IF(D15-C15&gt;TIME(9,0,0),TIME(1,0,0),IF(D15-C15&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A15,2)&gt;=6,J15=0),"",MIN(TIME(8,0,0),J15-F15))</f>
         <v/>
       </c>
       <c r="F15" s="12">
-        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,D15-C15-E15),0)</f>
-        <v/>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="12">
-        <f>IFERROR(MIN(F15,MAX(0,SUMIFS(F$4:F15,K$4:K15,K15)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I15" s="12">
-        <f>IFERROR(IF(F15=0,0,MAX(0,MIN(D15,29/24)-MAX(C15,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="10">
+        <f>IFERROR(MIN(J15,MAX(0,SUMIFS(J$4:J15,I$4:I15,I15)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="12">
+        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,IF(D15-C15&gt;TIME(9,0,0),TIME(1,0,0),IF(D15-C15&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="10">
         <f>IFERROR(A15-WEEKDAY(A15,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="12">
+        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,D15-C15-G15),0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="12">
+        <f>IFERROR(IF(OR(C15="",D15="",D15&lt;=C15),0,MAX(0,MIN(D15,29/24)-MAX(C15,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3794,35 +3915,36 @@
         <v>0.4583333333333333</v>
       </c>
       <c r="E16" s="12">
-        <f>IFERROR(IF(D16-C16&gt;TIME(9,0,0),TIME(1,0,0),IF(D16-C16&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A16,2)&gt;=6,J16=0),"",MIN(TIME(8,0,0),J16-F16))</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,D16-C16-E16),0)</f>
-        <v/>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="12">
-        <f>IFERROR(MIN(F16,MAX(0,SUMIFS(F$4:F16,K$4:K16,K16)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="12">
-        <f>IFERROR(IF(F16=0,0,MAX(0,MIN(D16,29/24)-MAX(C16,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J16" s="11" t="inlineStr"/>
-      <c r="K16" s="10">
+        <f>IFERROR(MIN(J16,MAX(0,SUMIFS(J$4:J16,I$4:I16,I16)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="12">
+        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,IF(D16-C16&gt;TIME(9,0,0),TIME(1,0,0),IF(D16-C16&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="11" t="inlineStr"/>
+      <c r="I16" s="10">
         <f>IFERROR(A16-WEEKDAY(A16,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J16" s="12">
+        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,D16-C16-G16),0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="12">
+        <f>IFERROR(IF(OR(C16="",D16="",D16&lt;=C16),0,MAX(0,MIN(D16,29/24)-MAX(C16,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="13" t="n">
         <v>46095</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="14">
         <f>TEXT(A17,"aaa")</f>
         <v/>
       </c>
@@ -3832,67 +3954,69 @@
       <c r="D17" s="8" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="E17" s="12">
-        <f>IFERROR(IF(D17-C17&gt;TIME(9,0,0),TIME(1,0,0),IF(D17-C17&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
-        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,D17-C17-E17),0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="12">
-        <f>IFERROR(MIN(F17,MAX(0,SUMIFS(F$4:F17,K$4:K17,K17)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="12">
-        <f>IFERROR(IF(F17=0,0,MAX(0,MIN(D17,29/24)-MAX(C17,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J17" s="11" t="inlineStr"/>
-      <c r="K17" s="10">
+      <c r="E17" s="15">
+        <f>IF(OR(WEEKDAY(A17,2)&gt;=6,J17=0),"",MIN(TIME(8,0,0),J17-F17))</f>
+        <v/>
+      </c>
+      <c r="F17" s="15">
+        <f>IFERROR(MIN(J17,MAX(0,SUMIFS(J$4:J17,I$4:I17,I17)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="15">
+        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,IF(D17-C17&gt;TIME(9,0,0),TIME(1,0,0),IF(D17-C17&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="13">
         <f>IFERROR(A17-WEEKDAY(A17,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J17" s="15">
+        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,D17-C17-G17),0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="15">
+        <f>IFERROR(IF(OR(C17="",D17="",D17&lt;=C17),0,MAX(0,MIN(D17,29/24)-MAX(C17,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n">
+      <c r="A18" s="16" t="n">
         <v>46096</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="17">
         <f>TEXT(A18,"aaa")</f>
         <v/>
       </c>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
-      <c r="E18" s="15">
-        <f>IFERROR(IF(D18-C18&gt;TIME(9,0,0),TIME(1,0,0),IF(D18-C18&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="15">
-        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,D18-C18-E18),0)</f>
-        <v/>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="15">
-        <f>IFERROR(MIN(F18,MAX(0,SUMIFS(F$4:F18,K$4:K18,K18)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I18" s="15">
-        <f>IFERROR(IF(F18=0,0,MAX(0,MIN(D18,29/24)-MAX(C18,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="E18" s="18">
+        <f>IF(OR(WEEKDAY(A18,2)&gt;=6,J18=0),"",MIN(TIME(8,0,0),J18-F18))</f>
+        <v/>
+      </c>
+      <c r="F18" s="18">
+        <f>IFERROR(MIN(J18,MAX(0,SUMIFS(J$4:J18,I$4:I18,I18)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="18">
+        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,IF(D18-C18&gt;TIME(9,0,0),TIME(1,0,0),IF(D18-C18&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K18" s="13">
+      <c r="I18" s="16">
         <f>IFERROR(A18-WEEKDAY(A18,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="18">
+        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,D18-C18-G18),0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="18">
+        <f>IFERROR(IF(OR(C18="",D18="",D18&lt;=C18),0,MAX(0,MIN(D18,29/24)-MAX(C18,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3911,27 +4035,28 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E19" s="12">
-        <f>IFERROR(IF(D19-C19&gt;TIME(9,0,0),TIME(1,0,0),IF(D19-C19&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A19,2)&gt;=6,J19=0),"",MIN(TIME(8,0,0),J19-F19))</f>
         <v/>
       </c>
       <c r="F19" s="12">
-        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,D19-C19-E19),0)</f>
-        <v/>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12">
-        <f>IFERROR(MIN(F19,MAX(0,SUMIFS(F$4:F19,K$4:K19,K19)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I19" s="12">
-        <f>IFERROR(IF(F19=0,0,MAX(0,MIN(D19,29/24)-MAX(C19,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="11" t="inlineStr"/>
-      <c r="K19" s="10">
+        <f>IFERROR(MIN(J19,MAX(0,SUMIFS(J$4:J19,I$4:I19,I19)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="12">
+        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,IF(D19-C19&gt;TIME(9,0,0),TIME(1,0,0),IF(D19-C19&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="10">
         <f>IFERROR(A19-WEEKDAY(A19,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="12">
+        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,D19-C19-G19),0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="12">
+        <f>IFERROR(IF(OR(C19="",D19="",D19&lt;=C19),0,MAX(0,MIN(D19,29/24)-MAX(C19,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3950,27 +4075,28 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E20" s="12">
-        <f>IFERROR(IF(D20-C20&gt;TIME(9,0,0),TIME(1,0,0),IF(D20-C20&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A20,2)&gt;=6,J20=0),"",MIN(TIME(8,0,0),J20-F20))</f>
         <v/>
       </c>
       <c r="F20" s="12">
-        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,D20-C20-E20),0)</f>
-        <v/>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="12">
-        <f>IFERROR(MIN(F20,MAX(0,SUMIFS(F$4:F20,K$4:K20,K20)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I20" s="12">
-        <f>IFERROR(IF(F20=0,0,MAX(0,MIN(D20,29/24)-MAX(C20,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="10">
+        <f>IFERROR(MIN(J20,MAX(0,SUMIFS(J$4:J20,I$4:I20,I20)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="12">
+        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,IF(D20-C20&gt;TIME(9,0,0),TIME(1,0,0),IF(D20-C20&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="11" t="inlineStr"/>
+      <c r="I20" s="10">
         <f>IFERROR(A20-WEEKDAY(A20,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="12">
+        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,D20-C20-G20),0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="12">
+        <f>IFERROR(IF(OR(C20="",D20="",D20&lt;=C20),0,MAX(0,MIN(D20,29/24)-MAX(C20,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -3989,27 +4115,28 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E21" s="12">
-        <f>IFERROR(IF(D21-C21&gt;TIME(9,0,0),TIME(1,0,0),IF(D21-C21&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A21,2)&gt;=6,J21=0),"",MIN(TIME(8,0,0),J21-F21))</f>
         <v/>
       </c>
       <c r="F21" s="12">
-        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,D21-C21-E21),0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="12">
-        <f>IFERROR(MIN(F21,MAX(0,SUMIFS(F$4:F21,K$4:K21,K21)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="12">
-        <f>IFERROR(IF(F21=0,0,MAX(0,MIN(D21,29/24)-MAX(C21,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="10">
+        <f>IFERROR(MIN(J21,MAX(0,SUMIFS(J$4:J21,I$4:I21,I21)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="12">
+        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,IF(D21-C21&gt;TIME(9,0,0),TIME(1,0,0),IF(D21-C21&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="11" t="inlineStr"/>
+      <c r="I21" s="10">
         <f>IFERROR(A21-WEEKDAY(A21,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="12">
+        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,D21-C21-G21),0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="12">
+        <f>IFERROR(IF(OR(C21="",D21="",D21&lt;=C21),0,MAX(0,MIN(D21,29/24)-MAX(C21,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -4028,27 +4155,28 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="E22" s="12">
-        <f>IFERROR(IF(D22-C22&gt;TIME(9,0,0),TIME(1,0,0),IF(D22-C22&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A22,2)&gt;=6,J22=0),"",MIN(TIME(8,0,0),J22-F22))</f>
         <v/>
       </c>
       <c r="F22" s="12">
-        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,D22-C22-E22),0)</f>
-        <v/>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="12">
-        <f>IFERROR(MIN(F22,MAX(0,SUMIFS(F$4:F22,K$4:K22,K22)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="12">
-        <f>IFERROR(IF(F22=0,0,MAX(0,MIN(D22,29/24)-MAX(C22,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="11" t="inlineStr"/>
-      <c r="K22" s="10">
+        <f>IFERROR(MIN(J22,MAX(0,SUMIFS(J$4:J22,I$4:I22,I22)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="12">
+        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,IF(D22-C22&gt;TIME(9,0,0),TIME(1,0,0),IF(D22-C22&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="11" t="inlineStr"/>
+      <c r="I22" s="10">
         <f>IFERROR(A22-WEEKDAY(A22,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,D22-C22-G22),0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="12">
+        <f>IFERROR(IF(OR(C22="",D22="",D22&lt;=C22),0,MAX(0,MIN(D22,29/24)-MAX(C22,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -4063,39 +4191,40 @@
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="9">
-        <f>IFERROR(IF(D23-C23&gt;TIME(9,0,0),TIME(1,0,0),IF(D23-C23&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A23,2)&gt;=6,J23=0),"",MIN(TIME(8,0,0),J23-F23))</f>
         <v/>
       </c>
       <c r="F23" s="9">
-        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,D23-C23-E23),0)</f>
-        <v/>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9">
-        <f>IFERROR(MIN(F23,MAX(0,SUMIFS(F$4:F23,K$4:K23,K23)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I23" s="9">
-        <f>IFERROR(IF(F23=0,0,MAX(0,MIN(D23,29/24)-MAX(C23,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+        <f>IFERROR(MIN(J23,MAX(0,SUMIFS(J$4:J23,I$4:I23,I23)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="9">
+        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,IF(D23-C23&gt;TIME(9,0,0),TIME(1,0,0),IF(D23-C23&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>春分の日</t>
         </is>
       </c>
-      <c r="K23" s="6">
+      <c r="I23" s="6">
         <f>IFERROR(A23-WEEKDAY(A23,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J23" s="9">
+        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,D23-C23-G23),0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="9">
+        <f>IFERROR(IF(OR(C23="",D23="",D23&lt;=C23),0,MAX(0,MIN(D23,29/24)-MAX(C23,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="13" t="n">
         <v>46102</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="14">
         <f>TEXT(A24,"aaa")</f>
         <v/>
       </c>
@@ -4105,67 +4234,69 @@
       <c r="D24" s="8" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="E24" s="12">
-        <f>IFERROR(IF(D24-C24&gt;TIME(9,0,0),TIME(1,0,0),IF(D24-C24&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F24" s="12">
-        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,D24-C24-E24),0)</f>
-        <v/>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="12">
-        <f>IFERROR(MIN(F24,MAX(0,SUMIFS(F$4:F24,K$4:K24,K24)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I24" s="12">
-        <f>IFERROR(IF(F24=0,0,MAX(0,MIN(D24,29/24)-MAX(C24,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="10">
+      <c r="E24" s="15">
+        <f>IF(OR(WEEKDAY(A24,2)&gt;=6,J24=0),"",MIN(TIME(8,0,0),J24-F24))</f>
+        <v/>
+      </c>
+      <c r="F24" s="15">
+        <f>IFERROR(MIN(J24,MAX(0,SUMIFS(J$4:J24,I$4:I24,I24)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="15">
+        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,IF(D24-C24&gt;TIME(9,0,0),TIME(1,0,0),IF(D24-C24&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="14" t="inlineStr"/>
+      <c r="I24" s="13">
         <f>IFERROR(A24-WEEKDAY(A24,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J24" s="15">
+        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,D24-C24-G24),0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="15">
+        <f>IFERROR(IF(OR(C24="",D24="",D24&lt;=C24),0,MAX(0,MIN(D24,29/24)-MAX(C24,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="n">
+      <c r="A25" s="16" t="n">
         <v>46103</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="17">
         <f>TEXT(A25,"aaa")</f>
         <v/>
       </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
-      <c r="E25" s="15">
-        <f>IFERROR(IF(D25-C25&gt;TIME(9,0,0),TIME(1,0,0),IF(D25-C25&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F25" s="15">
-        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,D25-C25-E25),0)</f>
-        <v/>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="15">
-        <f>IFERROR(MIN(F25,MAX(0,SUMIFS(F$4:F25,K$4:K25,K25)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I25" s="15">
-        <f>IFERROR(IF(F25=0,0,MAX(0,MIN(D25,29/24)-MAX(C25,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="E25" s="18">
+        <f>IF(OR(WEEKDAY(A25,2)&gt;=6,J25=0),"",MIN(TIME(8,0,0),J25-F25))</f>
+        <v/>
+      </c>
+      <c r="F25" s="18">
+        <f>IFERROR(MIN(J25,MAX(0,SUMIFS(J$4:J25,I$4:I25,I25)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="18">
+        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,IF(D25-C25&gt;TIME(9,0,0),TIME(1,0,0),IF(D25-C25&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K25" s="13">
+      <c r="I25" s="16">
         <f>IFERROR(A25-WEEKDAY(A25,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="18">
+        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,D25-C25-G25),0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="18">
+        <f>IFERROR(IF(OR(C25="",D25="",D25&lt;=C25),0,MAX(0,MIN(D25,29/24)-MAX(C25,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -4184,27 +4315,28 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="E26" s="12">
-        <f>IFERROR(IF(D26-C26&gt;TIME(9,0,0),TIME(1,0,0),IF(D26-C26&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A26,2)&gt;=6,J26=0),"",MIN(TIME(8,0,0),J26-F26))</f>
         <v/>
       </c>
       <c r="F26" s="12">
-        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,D26-C26-E26),0)</f>
-        <v/>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="12">
-        <f>IFERROR(MIN(F26,MAX(0,SUMIFS(F$4:F26,K$4:K26,K26)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I26" s="12">
-        <f>IFERROR(IF(F26=0,0,MAX(0,MIN(D26,29/24)-MAX(C26,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J26" s="11" t="inlineStr"/>
-      <c r="K26" s="10">
+        <f>IFERROR(MIN(J26,MAX(0,SUMIFS(J$4:J26,I$4:I26,I26)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="12">
+        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,IF(D26-C26&gt;TIME(9,0,0),TIME(1,0,0),IF(D26-C26&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="11" t="inlineStr"/>
+      <c r="I26" s="10">
         <f>IFERROR(A26-WEEKDAY(A26,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="12">
+        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,D26-C26-G26),0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="12">
+        <f>IFERROR(IF(OR(C26="",D26="",D26&lt;=C26),0,MAX(0,MIN(D26,29/24)-MAX(C26,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -4223,27 +4355,28 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="E27" s="12">
-        <f>IFERROR(IF(D27-C27&gt;TIME(9,0,0),TIME(1,0,0),IF(D27-C27&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A27,2)&gt;=6,J27=0),"",MIN(TIME(8,0,0),J27-F27))</f>
         <v/>
       </c>
       <c r="F27" s="12">
-        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,D27-C27-E27),0)</f>
-        <v/>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="12">
-        <f>IFERROR(MIN(F27,MAX(0,SUMIFS(F$4:F27,K$4:K27,K27)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I27" s="12">
-        <f>IFERROR(IF(F27=0,0,MAX(0,MIN(D27,29/24)-MAX(C27,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
-      <c r="K27" s="10">
+        <f>IFERROR(MIN(J27,MAX(0,SUMIFS(J$4:J27,I$4:I27,I27)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="12">
+        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,IF(D27-C27&gt;TIME(9,0,0),TIME(1,0,0),IF(D27-C27&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="11" t="inlineStr"/>
+      <c r="I27" s="10">
         <f>IFERROR(A27-WEEKDAY(A27,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="12">
+        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,D27-C27-G27),0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="12">
+        <f>IFERROR(IF(OR(C27="",D27="",D27&lt;=C27),0,MAX(0,MIN(D27,29/24)-MAX(C27,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -4262,27 +4395,28 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="E28" s="12">
-        <f>IFERROR(IF(D28-C28&gt;TIME(9,0,0),TIME(1,0,0),IF(D28-C28&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A28,2)&gt;=6,J28=0),"",MIN(TIME(8,0,0),J28-F28))</f>
         <v/>
       </c>
       <c r="F28" s="12">
-        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,D28-C28-E28),0)</f>
-        <v/>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="12">
-        <f>IFERROR(MIN(F28,MAX(0,SUMIFS(F$4:F28,K$4:K28,K28)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I28" s="12">
-        <f>IFERROR(IF(F28=0,0,MAX(0,MIN(D28,29/24)-MAX(C28,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J28" s="11" t="inlineStr"/>
-      <c r="K28" s="10">
+        <f>IFERROR(MIN(J28,MAX(0,SUMIFS(J$4:J28,I$4:I28,I28)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="12">
+        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,IF(D28-C28&gt;TIME(9,0,0),TIME(1,0,0),IF(D28-C28&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="11" t="inlineStr"/>
+      <c r="I28" s="10">
         <f>IFERROR(A28-WEEKDAY(A28,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="12">
+        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,D28-C28-G28),0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="12">
+        <f>IFERROR(IF(OR(C28="",D28="",D28&lt;=C28),0,MAX(0,MIN(D28,29/24)-MAX(C28,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -4301,27 +4435,28 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="E29" s="12">
-        <f>IFERROR(IF(D29-C29&gt;TIME(9,0,0),TIME(1,0,0),IF(D29-C29&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A29,2)&gt;=6,J29=0),"",MIN(TIME(8,0,0),J29-F29))</f>
         <v/>
       </c>
       <c r="F29" s="12">
-        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,D29-C29-E29),0)</f>
-        <v/>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="12">
-        <f>IFERROR(MIN(F29,MAX(0,SUMIFS(F$4:F29,K$4:K29,K29)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I29" s="12">
-        <f>IFERROR(IF(F29=0,0,MAX(0,MIN(D29,29/24)-MAX(C29,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J29" s="11" t="inlineStr"/>
-      <c r="K29" s="10">
+        <f>IFERROR(MIN(J29,MAX(0,SUMIFS(J$4:J29,I$4:I29,I29)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="12">
+        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,IF(D29-C29&gt;TIME(9,0,0),TIME(1,0,0),IF(D29-C29&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="11" t="inlineStr"/>
+      <c r="I29" s="10">
         <f>IFERROR(A29-WEEKDAY(A29,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="12">
+        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,D29-C29-G29),0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="12">
+        <f>IFERROR(IF(OR(C29="",D29="",D29&lt;=C29),0,MAX(0,MIN(D29,29/24)-MAX(C29,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -4340,35 +4475,36 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="E30" s="12">
-        <f>IFERROR(IF(D30-C30&gt;TIME(9,0,0),TIME(1,0,0),IF(D30-C30&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A30,2)&gt;=6,J30=0),"",MIN(TIME(8,0,0),J30-F30))</f>
         <v/>
       </c>
       <c r="F30" s="12">
-        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,D30-C30-E30),0)</f>
-        <v/>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="12">
-        <f>IFERROR(MIN(F30,MAX(0,SUMIFS(F$4:F30,K$4:K30,K30)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I30" s="12">
-        <f>IFERROR(IF(F30=0,0,MAX(0,MIN(D30,29/24)-MAX(C30,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J30" s="11" t="inlineStr"/>
-      <c r="K30" s="10">
+        <f>IFERROR(MIN(J30,MAX(0,SUMIFS(J$4:J30,I$4:I30,I30)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="12">
+        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,IF(D30-C30&gt;TIME(9,0,0),TIME(1,0,0),IF(D30-C30&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="11" t="inlineStr"/>
+      <c r="I30" s="10">
         <f>IFERROR(A30-WEEKDAY(A30,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J30" s="12">
+        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,D30-C30-G30),0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="12">
+        <f>IFERROR(IF(OR(C30="",D30="",D30&lt;=C30),0,MAX(0,MIN(D30,29/24)-MAX(C30,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="13" t="n">
         <v>46109</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="14">
         <f>TEXT(A31,"aaa")</f>
         <v/>
       </c>
@@ -4378,67 +4514,69 @@
       <c r="D31" s="8" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="E31" s="12">
-        <f>IFERROR(IF(D31-C31&gt;TIME(9,0,0),TIME(1,0,0),IF(D31-C31&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F31" s="12">
-        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,D31-C31-E31),0)</f>
-        <v/>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="12">
-        <f>IFERROR(MIN(F31,MAX(0,SUMIFS(F$4:F31,K$4:K31,K31)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I31" s="12">
-        <f>IFERROR(IF(F31=0,0,MAX(0,MIN(D31,29/24)-MAX(C31,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J31" s="11" t="inlineStr"/>
-      <c r="K31" s="10">
+      <c r="E31" s="15">
+        <f>IF(OR(WEEKDAY(A31,2)&gt;=6,J31=0),"",MIN(TIME(8,0,0),J31-F31))</f>
+        <v/>
+      </c>
+      <c r="F31" s="15">
+        <f>IFERROR(MIN(J31,MAX(0,SUMIFS(J$4:J31,I$4:I31,I31)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="15">
+        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,IF(D31-C31&gt;TIME(9,0,0),TIME(1,0,0),IF(D31-C31&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="14" t="inlineStr"/>
+      <c r="I31" s="13">
         <f>IFERROR(A31-WEEKDAY(A31,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J31" s="15">
+        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,D31-C31-G31),0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="15">
+        <f>IFERROR(IF(OR(C31="",D31="",D31&lt;=C31),0,MAX(0,MIN(D31,29/24)-MAX(C31,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="n">
+      <c r="A32" s="16" t="n">
         <v>46110</v>
       </c>
-      <c r="B32" s="14">
+      <c r="B32" s="17">
         <f>TEXT(A32,"aaa")</f>
         <v/>
       </c>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="n"/>
-      <c r="E32" s="15">
-        <f>IFERROR(IF(D32-C32&gt;TIME(9,0,0),TIME(1,0,0),IF(D32-C32&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
-        <v/>
-      </c>
-      <c r="F32" s="15">
-        <f>IFERROR(IF(OR(C32="",D32="",D32&lt;=C32),0,D32-C32-E32),0)</f>
-        <v/>
-      </c>
-      <c r="G32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="15">
-        <f>IFERROR(MIN(F32,MAX(0,SUMIFS(F$4:F32,K$4:K32,K32)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I32" s="15">
-        <f>IFERROR(IF(F32=0,0,MAX(0,MIN(D32,29/24)-MAX(C32,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="E32" s="18">
+        <f>IF(OR(WEEKDAY(A32,2)&gt;=6,J32=0),"",MIN(TIME(8,0,0),J32-F32))</f>
+        <v/>
+      </c>
+      <c r="F32" s="18">
+        <f>IFERROR(MIN(J32,MAX(0,SUMIFS(J$4:J32,I$4:I32,I32)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="18">
+        <f>IFERROR(IF(OR(C32="",D32="",D32&lt;=C32),0,IF(D32-C32&gt;TIME(9,0,0),TIME(1,0,0),IF(D32-C32&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>日曜</t>
         </is>
       </c>
-      <c r="K32" s="13">
+      <c r="I32" s="16">
         <f>IFERROR(A32-WEEKDAY(A32,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="18">
+        <f>IFERROR(IF(OR(C32="",D32="",D32&lt;=C32),0,D32-C32-G32),0)</f>
+        <v/>
+      </c>
+      <c r="K32" s="18">
+        <f>IFERROR(IF(OR(C32="",D32="",D32&lt;=C32),0,MAX(0,MIN(D32,29/24)-MAX(C32,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -4457,27 +4595,28 @@
         <v>0.4479166666666667</v>
       </c>
       <c r="E33" s="12">
-        <f>IFERROR(IF(D33-C33&gt;TIME(9,0,0),TIME(1,0,0),IF(D33-C33&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A33,2)&gt;=6,J33=0),"",MIN(TIME(8,0,0),J33-F33))</f>
         <v/>
       </c>
       <c r="F33" s="12">
-        <f>IFERROR(IF(OR(C33="",D33="",D33&lt;=C33),0,D33-C33-E33),0)</f>
-        <v/>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="12">
-        <f>IFERROR(MIN(F33,MAX(0,SUMIFS(F$4:F33,K$4:K33,K33)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I33" s="12">
-        <f>IFERROR(IF(F33=0,0,MAX(0,MIN(D33,29/24)-MAX(C33,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J33" s="11" t="inlineStr"/>
-      <c r="K33" s="10">
+        <f>IFERROR(MIN(J33,MAX(0,SUMIFS(J$4:J33,I$4:I33,I33)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="12">
+        <f>IFERROR(IF(OR(C33="",D33="",D33&lt;=C33),0,IF(D33-C33&gt;TIME(9,0,0),TIME(1,0,0),IF(D33-C33&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H33" s="11" t="inlineStr"/>
+      <c r="I33" s="10">
         <f>IFERROR(A33-WEEKDAY(A33,2)+1,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="12">
+        <f>IFERROR(IF(OR(C33="",D33="",D33&lt;=C33),0,D33-C33-G33),0)</f>
+        <v/>
+      </c>
+      <c r="K33" s="12">
+        <f>IFERROR(IF(OR(C33="",D33="",D33&lt;=C33),0,MAX(0,MIN(D33,29/24)-MAX(C33,22/24))),0)</f>
         <v/>
       </c>
     </row>
@@ -4496,66 +4635,85 @@
         <v>0.4479166666666667</v>
       </c>
       <c r="E34" s="12">
-        <f>IFERROR(IF(D34-C34&gt;TIME(9,0,0),TIME(1,0,0),IF(D34-C34&gt;TIME(6,0,0),TIME(0,45,0),0)),0)</f>
+        <f>IF(OR(WEEKDAY(A34,2)&gt;=6,J34=0),"",MIN(TIME(8,0,0),J34-F34))</f>
         <v/>
       </c>
       <c r="F34" s="12">
-        <f>IFERROR(IF(OR(C34="",D34="",D34&lt;=C34),0,D34-C34-E34),0)</f>
-        <v/>
-      </c>
-      <c r="G34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="12">
-        <f>IFERROR(MIN(F34,MAX(0,SUMIFS(F$4:F34,K$4:K34,K34)-TIME(0,0,0)-40/24)),0)</f>
-        <v/>
-      </c>
-      <c r="I34" s="12">
-        <f>IFERROR(IF(F34=0,0,MAX(0,MIN(D34,29/24)-MAX(C34,22/24))),0)</f>
-        <v/>
-      </c>
-      <c r="J34" s="11" t="inlineStr"/>
-      <c r="K34" s="10">
+        <f>IFERROR(MIN(J34,MAX(0,SUMIFS(J$4:J34,I$4:I34,I34)-40/24)),0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="12">
+        <f>IFERROR(IF(OR(C34="",D34="",D34&lt;=C34),0,IF(D34-C34&gt;TIME(9,0,0),TIME(1,0,0),IF(D34-C34&gt;TIME(6,0,0),TIME(0,45,0),0))),0)</f>
+        <v/>
+      </c>
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="10">
         <f>IFERROR(A34-WEEKDAY(A34,2)+1,"")</f>
         <v/>
       </c>
+      <c r="J34" s="12">
+        <f>IFERROR(IF(OR(C34="",D34="",D34&lt;=C34),0,D34-C34-G34),0)</f>
+        <v/>
+      </c>
+      <c r="K34" s="12">
+        <f>IFERROR(IF(OR(C34="",D34="",D34&lt;=C34),0,MAX(0,MIN(D34,29/24)-MAX(C34,22/24))),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B35" s="16">
-        <f>COUNTIF(F4:F34,"&gt;0")&amp;"日"</f>
-        <v/>
-      </c>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="17">
+      <c r="B35" s="19">
+        <f>COUNTIF(J4:J34,"&gt;0")&amp;"日"</f>
+        <v/>
+      </c>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="20">
+        <f>SUM(E4:E34)</f>
+        <v/>
+      </c>
+      <c r="F35" s="20">
         <f>SUM(F4:F34)</f>
         <v/>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="20">
         <f>SUM(G4:G34)</f>
         <v/>
       </c>
-      <c r="H35" s="17">
-        <f>SUM(H4:H34)</f>
-        <v/>
-      </c>
-      <c r="I35" s="17">
-        <f>SUM(I4:I34)</f>
-        <v/>
-      </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="19" t="n"/>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="19" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>総労働時間</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="20">
+        <f>SUM(J4:J34)</f>
+        <v/>
+      </c>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="19" t="n"/>
+      <c r="H36" s="19" t="n"/>
+      <c r="I36" s="19" t="n"/>
+      <c r="J36" s="19" t="n"/>
+      <c r="K36" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+  <mergeCells count="3">
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
